--- a/data/数据库表导出_v3.xlsx
+++ b/data/数据库表导出_v3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080" tabRatio="873" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="12080" tabRatio="873" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="fund_info(基金基本信息表)" sheetId="1" r:id="rId1"/>
@@ -61,6 +61,26 @@
 基金分类</t>
   </si>
   <si>
+    <t>return_1y
+近1年收益率</t>
+  </si>
+  <si>
+    <t>return_3y
+近3年收益率</t>
+  </si>
+  <si>
+    <t>return_since_inception
+成立以来收益率</t>
+  </si>
+  <si>
+    <t>created_at
+创建时间</t>
+  </si>
+  <si>
+    <t>updated_at
+更新时间</t>
+  </si>
+  <si>
     <t>top_holdings
 前十大持仓</t>
   </si>
@@ -69,26 +89,6 @@
 风险提示要点</t>
   </si>
   <si>
-    <t>return_1y
-近1年收益率</t>
-  </si>
-  <si>
-    <t>return_3y
-近3年收益率</t>
-  </si>
-  <si>
-    <t>return_since_inception
-成立以来收益率</t>
-  </si>
-  <si>
-    <t>created_at
-创建时间</t>
-  </si>
-  <si>
-    <t>updated_at
-更新时间</t>
-  </si>
-  <si>
     <t>广发天天红货币B</t>
   </si>
   <si>
@@ -107,24 +107,24 @@
     <t>货币基金</t>
   </si>
   <si>
+    <t>1.43%</t>
+  </si>
+  <si>
+    <t>5.52%</t>
+  </si>
+  <si>
+    <t>29.77%</t>
+  </si>
+  <si>
+    <t>2026-03-05 21:14:27</t>
+  </si>
+  <si>
     <t>22国开14(1.26%)、24建设银行CD104(1.02%)、23国开14(0.67%)、24民生银行CD230(0.66%)、24民生银行CD306(0.58%)</t>
   </si>
   <si>
     <t>低风险，流动性强</t>
   </si>
   <si>
-    <t>1.43%</t>
-  </si>
-  <si>
-    <t>5.52%</t>
-  </si>
-  <si>
-    <t>29.77%</t>
-  </si>
-  <si>
-    <t>2026-03-05 21:14:27</t>
-  </si>
-  <si>
     <t>广发中证军工ETF联接C</t>
   </si>
   <si>
@@ -143,24 +143,24 @@
     <t>军工</t>
   </si>
   <si>
+    <t>+40.63%</t>
+  </si>
+  <si>
+    <t>+29.38%</t>
+  </si>
+  <si>
+    <t>+99.75%</t>
+  </si>
+  <si>
+    <t>2026-03-05 20:38:14</t>
+  </si>
+  <si>
     <t>主要投资于广发中证军工ETF,重仓股包括中国船舶、光启技术、航天电子等军工股</t>
   </si>
   <si>
     <t>军工板块政策依赖,地缘政治敏感,订单波动风险</t>
   </si>
   <si>
-    <t>+40.63%</t>
-  </si>
-  <si>
-    <t>+29.38%</t>
-  </si>
-  <si>
-    <t>+99.75%</t>
-  </si>
-  <si>
-    <t>2026-03-05 20:38:14</t>
-  </si>
-  <si>
     <t>华夏黄金ETF联接C</t>
   </si>
   <si>
@@ -173,24 +173,24 @@
     <t>黄金</t>
   </si>
   <si>
+    <t>+75.04%</t>
+  </si>
+  <si>
+    <t>+122.66%</t>
+  </si>
+  <si>
+    <t>+159.31%</t>
+  </si>
+  <si>
+    <t>2026-03-05 20:45:43</t>
+  </si>
+  <si>
     <t>主要投资于目标ETF(华夏黄金ETF),间接跟踪黄金9999价格</t>
   </si>
   <si>
     <t>国际金价波动风险,汇率风险</t>
   </si>
   <si>
-    <t>+75.04%</t>
-  </si>
-  <si>
-    <t>+122.66%</t>
-  </si>
-  <si>
-    <t>+159.31%</t>
-  </si>
-  <si>
-    <t>2026-03-05 20:45:43</t>
-  </si>
-  <si>
     <t>建信上海金ETF联接C</t>
   </si>
   <si>
@@ -200,54 +200,54 @@
     <t>上海金(SHAU)</t>
   </si>
   <si>
+    <t>+74.38%</t>
+  </si>
+  <si>
+    <t>+172.87%</t>
+  </si>
+  <si>
+    <t>+173.03%</t>
+  </si>
+  <si>
     <t>主要投资于目标ETF(建信上海金ETF),间接跟踪上海金价格</t>
   </si>
   <si>
-    <t>+74.38%</t>
-  </si>
-  <si>
-    <t>+172.87%</t>
-  </si>
-  <si>
-    <t>+173.03%</t>
-  </si>
-  <si>
     <t>富国上海金ETF联接C</t>
   </si>
   <si>
     <t>富国基金</t>
   </si>
   <si>
+    <t>+67.15%</t>
+  </si>
+  <si>
+    <t>+156.27%</t>
+  </si>
+  <si>
+    <t>+140.66%</t>
+  </si>
+  <si>
     <t>主要投资于目标ETF(富国上海金ETF),间接跟踪上海金价格</t>
   </si>
   <si>
-    <t>+67.15%</t>
-  </si>
-  <si>
-    <t>+156.27%</t>
-  </si>
-  <si>
-    <t>+140.66%</t>
-  </si>
-  <si>
     <t>天弘上海金ETF联接C</t>
   </si>
   <si>
     <t>天弘基金</t>
   </si>
   <si>
+    <t>+65.35%</t>
+  </si>
+  <si>
+    <t>+148.75%</t>
+  </si>
+  <si>
+    <t>+155.87%</t>
+  </si>
+  <si>
     <t>主要投资于目标ETF(天弘上海金ETF),间接跟踪上海金价格</t>
   </si>
   <si>
-    <t>+65.35%</t>
-  </si>
-  <si>
-    <t>+148.75%</t>
-  </si>
-  <si>
-    <t>+155.87%</t>
-  </si>
-  <si>
     <t>天弘中证机器人ETF联接C</t>
   </si>
   <si>
@@ -257,21 +257,21 @@
     <t>机器人</t>
   </si>
   <si>
+    <t>+11.39%</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>+24.90%</t>
+  </si>
+  <si>
     <t>主要投资于天弘中证机器人ETF,重仓股包括科大讯飞9.76%,汇川技术9.71%,拓普集团7.91%等</t>
   </si>
   <si>
     <t>机器人产业波动大,技术迭代风险,联接基金双重收费</t>
   </si>
   <si>
-    <t>+11.39%</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>+24.90%</t>
-  </si>
-  <si>
     <t>嘉实上证科创板芯片ETF联接C</t>
   </si>
   <si>
@@ -284,66 +284,66 @@
     <t>芯片</t>
   </si>
   <si>
+    <t>+107.37%</t>
+  </si>
+  <si>
+    <t>+106.87%</t>
+  </si>
+  <si>
     <t>主要投资于科创芯片ETF,重仓股包括中芯国际10.36%,海光信息10.05%,寒武纪9.45%,澜起科技7.73%等</t>
   </si>
   <si>
     <t>科创板估值高,芯片技术封锁风险,波动剧烈</t>
   </si>
   <si>
-    <t>+107.37%</t>
-  </si>
-  <si>
-    <t>+106.87%</t>
-  </si>
-  <si>
     <t>华夏中证机器人ETF联接C</t>
   </si>
   <si>
+    <t>+5.13%</t>
+  </si>
+  <si>
+    <t>+29.84%</t>
+  </si>
+  <si>
     <t>主要投资于华夏中证机器人ETF,重仓股包括科大讯飞、汇川技术等</t>
   </si>
   <si>
-    <t>+5.13%</t>
-  </si>
-  <si>
-    <t>+29.84%</t>
-  </si>
-  <si>
     <t>工银瑞信黄金ETF联接E</t>
   </si>
   <si>
     <t>工银瑞信基金</t>
   </si>
   <si>
+    <t>+67.85%</t>
+  </si>
+  <si>
+    <t>+129.85%</t>
+  </si>
+  <si>
     <t>主要投资于目标ETF(工银黄金ETF),间接跟踪黄金9999价格</t>
   </si>
   <si>
     <t>国际金价波动风险,汇率风险,成立时间短</t>
   </si>
   <si>
-    <t>+67.85%</t>
-  </si>
-  <si>
-    <t>+129.85%</t>
-  </si>
-  <si>
     <t>招商中证机器人ETF联接C</t>
   </si>
   <si>
     <t>招商基金</t>
   </si>
   <si>
+    <t>+7.45%</t>
+  </si>
+  <si>
+    <t>+62.35%</t>
+  </si>
+  <si>
     <t>主要投资于招商中证机器人ETF,重仓股包括科大讯飞9.76%,汇川技术9.71%,拓普集团7.91%等</t>
   </si>
   <si>
     <t>机器人产业波动大,技术迭代风险,联接基金双重收费,成立时间短</t>
   </si>
   <si>
-    <t>+7.45%</t>
-  </si>
-  <si>
-    <t>+62.35%</t>
-  </si>
-  <si>
     <t>华夏国证航天航空行业ETF</t>
   </si>
   <si>
@@ -356,24 +356,24 @@
     <t>航空航天</t>
   </si>
   <si>
+    <t>+47.66%</t>
+  </si>
+  <si>
     <t>光启技术9.12%,中国卫星6.71%,航天电子6.47%,航发动力6.51%,中航沈飞5.93%,航天发展5.00%,中航西飞3.89%,中航机载3.61%,上海瀚讯2.65%,中航成飞2.60%</t>
   </si>
   <si>
     <t>军工板块政策依赖,地缘政治敏感</t>
   </si>
   <si>
-    <t>+47.66%</t>
-  </si>
-  <si>
     <t>天弘国证航天航空行业ETF</t>
   </si>
   <si>
+    <t>+60%</t>
+  </si>
+  <si>
     <t>光启技术9.20%,中国卫星6.78%,航天电子6.51%,航发动力6.51%,中航沈飞5.93%,航天发展5.00%,中航西飞3.89%,中航机载3.61%,上海瀚讯2.65%,中航成飞2.60%</t>
   </si>
   <si>
-    <t>+60%</t>
-  </si>
-  <si>
     <t>易方达国证机器人产业ETF</t>
   </si>
   <si>
@@ -383,33 +383,33 @@
     <t>国证机器人产业指数</t>
   </si>
   <si>
+    <t>+23.11%</t>
+  </si>
+  <si>
+    <t>+60.15%</t>
+  </si>
+  <si>
     <t>绿的谐波5.59%,双环传动5.30%,机器人4.70%,石头科技4.53%,科沃斯3.69%,三花智控3.28%,拓普集团3.15%,鸣志电器3.13%,领益智造2.88%,科大讯飞2.86%</t>
   </si>
   <si>
     <t>机器人产业波动大,技术迭代风险,集中度高</t>
   </si>
   <si>
-    <t>+23.11%</t>
-  </si>
-  <si>
-    <t>+60.15%</t>
-  </si>
-  <si>
     <t>天弘中证机器人ETF</t>
   </si>
   <si>
+    <t>+21.36%</t>
+  </si>
+  <si>
+    <t>+11.94%</t>
+  </si>
+  <si>
     <t>科大讯飞9.75%,汇川技术9.73%,拓普集团7.93%,大华股份4.41%,大族激光4.01%,双环传动3.81%,石头科技3.73%,中控技术3.69%,绿的谐波2.92%,机器人2.69%</t>
   </si>
   <si>
     <t>机器人产业波动大,技术迭代风险</t>
   </si>
   <si>
-    <t>+21.36%</t>
-  </si>
-  <si>
-    <t>+11.94%</t>
-  </si>
-  <si>
     <t>易方达中证科创创业50ETF</t>
   </si>
   <si>
@@ -419,18 +419,18 @@
     <t>科创</t>
   </si>
   <si>
+    <t>+54.94%</t>
+  </si>
+  <si>
+    <t>-5.67%</t>
+  </si>
+  <si>
     <t>中际旭创10.73%,新易盛10.16%,宁德时代9.38%,寒武纪6.79%,阳光电源5.89%,中芯国际5.83%,海光信息4.95%,胜宏科技4.16%,汇川技术3.38%,澜起科技3.20%</t>
   </si>
   <si>
     <t>科创板估值高,波动剧烈,技术封锁风险</t>
   </si>
   <si>
-    <t>+54.94%</t>
-  </si>
-  <si>
-    <t>-5.67%</t>
-  </si>
-  <si>
     <t>富国中证港股通互联网ETF</t>
   </si>
   <si>
@@ -440,13 +440,13 @@
     <t>互联网</t>
   </si>
   <si>
+    <t>-27.24%</t>
+  </si>
+  <si>
     <t>腾讯控股15.37%,阿里巴巴-W14.46%,小米集团-W13.99%,美团-W12.32%,商汤-W4.09%,快手-W3.78%,贝壳-W3.74%,京东健康3.72%,哔哩哔哩-W3.30%,金蝶国际-</t>
   </si>
   <si>
     <t>港股汇率风险,监管政策风险,流动性风险</t>
-  </si>
-  <si>
-    <t>-27.24%</t>
   </si>
   <si>
     <t>002183</t>
@@ -568,37 +568,37 @@
 最后更新日期</t>
   </si>
   <si>
+    <t>支付宝</t>
+  </si>
+  <si>
+    <t>每天定投100</t>
+  </si>
+  <si>
+    <t>固定金额</t>
+  </si>
+  <si>
+    <t>每周二定投200</t>
+  </si>
+  <si>
+    <t>每周五定投200</t>
+  </si>
+  <si>
+    <t>每周三定投200</t>
+  </si>
+  <si>
+    <t>每周一定投200</t>
+  </si>
+  <si>
+    <t>每周二智能定投100-400不等</t>
+  </si>
+  <si>
+    <t>智能定投</t>
+  </si>
+  <si>
+    <t>每周四定投200</t>
+  </si>
+  <si>
     <t>涨乐财富通</t>
-  </si>
-  <si>
-    <t>支付宝</t>
-  </si>
-  <si>
-    <t>每天定投100</t>
-  </si>
-  <si>
-    <t>固定金额</t>
-  </si>
-  <si>
-    <t>每周二定投200</t>
-  </si>
-  <si>
-    <t>每周五定投200</t>
-  </si>
-  <si>
-    <t>每周三定投200</t>
-  </si>
-  <si>
-    <t>每周一定投200</t>
-  </si>
-  <si>
-    <t>每周二智能定投100-400不等</t>
-  </si>
-  <si>
-    <t>智能定投</t>
-  </si>
-  <si>
-    <t>每周四定投200</t>
   </si>
   <si>
     <t>国债理财</t>
@@ -1859,7 +1859,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1874,6 +1874,19 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -2004,7 +2017,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -2016,34 +2029,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
@@ -2128,7 +2141,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2175,6 +2188,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2196,11 +2212,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2554,15 +2576,18 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.4545454545455" customWidth="1"/>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
+    <col min="2" max="2" width="29.8181818181818" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="10.4545454545455" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="11.5454545454545" customWidth="1"/>
     <col min="7" max="7" width="14.8181818181818" customWidth="1"/>
-    <col min="8" max="9" width="30" customWidth="1"/>
-    <col min="10" max="11" width="20" customWidth="1"/>
-    <col min="12" max="14" width="30" customWidth="1"/>
+    <col min="8" max="9" width="12.1818181818182" customWidth="1"/>
+    <col min="10" max="10" width="25.0909090909091" customWidth="1"/>
+    <col min="11" max="11" width="21.9090909090909" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="156.909090909091" customWidth="1"/>
+    <col min="14" max="14" width="64.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14">
@@ -2584,7 +2609,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="31" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -2629,7 +2654,7 @@
       <c r="F2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="32" t="s">
         <v>19</v>
       </c>
       <c r="H2" s="19" t="s">
@@ -2645,13 +2670,13 @@
         <v>23</v>
       </c>
       <c r="L2" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="N2" s="19" t="s">
         <v>25</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -2674,7 +2699,7 @@
       <c r="F3" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H3" s="19" t="s">
@@ -2690,13 +2715,13 @@
         <v>35</v>
       </c>
       <c r="L3" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="N3" s="19" t="s">
         <v>37</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -2719,7 +2744,7 @@
       <c r="F4" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="32" t="s">
         <v>41</v>
       </c>
       <c r="H4" s="19" t="s">
@@ -2732,13 +2757,13 @@
         <v>44</v>
       </c>
       <c r="K4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="M4" s="19" t="s">
         <v>46</v>
-      </c>
-      <c r="M4" s="19" t="s">
-        <v>37</v>
       </c>
       <c r="N4" s="19" t="s">
         <v>47</v>
@@ -2764,29 +2789,29 @@
       <c r="F5" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="32" t="s">
         <v>41</v>
       </c>
       <c r="H5" s="19" t="s">
         <v>51</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="L5" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="M5" s="19" t="s">
-        <v>37</v>
-      </c>
       <c r="N5" s="19" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2809,29 +2834,29 @@
       <c r="F6" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="32" t="s">
         <v>41</v>
       </c>
       <c r="H6" s="19" t="s">
         <v>57</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L6" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="M6" s="19" t="s">
-        <v>37</v>
-      </c>
       <c r="N6" s="19" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2854,26 +2879,26 @@
       <c r="F7" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="32" t="s">
         <v>41</v>
       </c>
       <c r="H7" s="19" t="s">
         <v>63</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="L7" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="19" t="s">
         <v>66</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>37</v>
       </c>
       <c r="N7" s="19" t="s">
         <v>47</v>
@@ -2899,7 +2924,7 @@
       <c r="F8" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H8" s="19" t="s">
@@ -2912,16 +2937,16 @@
         <v>72</v>
       </c>
       <c r="K8" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="N8" s="19" t="s">
         <v>74</v>
-      </c>
-      <c r="M8" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2944,29 +2969,29 @@
       <c r="F9" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="32" t="s">
         <v>78</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>79</v>
       </c>
       <c r="I9" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="K9" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L9" s="19" t="s">
+      <c r="N9" s="19" t="s">
         <v>82</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N9" s="19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2989,7 +3014,7 @@
       <c r="F10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H10" s="19" t="s">
@@ -3002,16 +3027,16 @@
         <v>85</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L10" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M10" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="M10" s="19" t="s">
-        <v>37</v>
-      </c>
       <c r="N10" s="19" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -3034,29 +3059,29 @@
       <c r="F11" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="32" t="s">
         <v>41</v>
       </c>
       <c r="H11" s="19" t="s">
         <v>89</v>
       </c>
       <c r="I11" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="K11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L11" s="19" t="s">
+      <c r="N11" s="19" t="s">
         <v>92</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3079,29 +3104,29 @@
       <c r="F12" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H12" s="19" t="s">
         <v>95</v>
       </c>
       <c r="I12" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="19" t="s">
+      <c r="K12" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="K12" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L12" s="19" t="s">
+      <c r="N12" s="19" t="s">
         <v>98</v>
-      </c>
-      <c r="M12" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N12" s="19" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3124,29 +3149,29 @@
       <c r="F13" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="32" t="s">
         <v>102</v>
       </c>
       <c r="H13" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="I13" s="19" t="s">
+      <c r="K13" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="J13" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L13" s="19" t="s">
+      <c r="N13" s="19" t="s">
         <v>105</v>
-      </c>
-      <c r="M13" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N13" s="19" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -3169,29 +3194,29 @@
       <c r="F14" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="32" t="s">
         <v>102</v>
       </c>
       <c r="H14" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="I14" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>73</v>
-      </c>
       <c r="K14" s="19" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L14" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="M14" s="19" t="s">
-        <v>37</v>
-      </c>
       <c r="N14" s="19" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -3214,29 +3239,29 @@
       <c r="F15" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H15" s="19" t="s">
         <v>112</v>
       </c>
       <c r="I15" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="J15" s="19" t="s">
+      <c r="K15" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M15" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="K15" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L15" s="19" t="s">
+      <c r="N15" s="19" t="s">
         <v>115</v>
-      </c>
-      <c r="M15" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N15" s="19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -3259,29 +3284,29 @@
       <c r="F16" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="19" t="s">
         <v>117</v>
       </c>
       <c r="I16" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="J16" s="19" t="s">
+      <c r="K16" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M16" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="K16" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L16" s="19" t="s">
+      <c r="N16" s="19" t="s">
         <v>120</v>
-      </c>
-      <c r="M16" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16" s="19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -3304,29 +3329,29 @@
       <c r="F17" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="32" t="s">
         <v>123</v>
       </c>
       <c r="H17" s="19" t="s">
         <v>124</v>
       </c>
       <c r="I17" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="J17" s="19" t="s">
+      <c r="K17" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M17" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="K17" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L17" s="19" t="s">
+      <c r="N17" s="19" t="s">
         <v>127</v>
-      </c>
-      <c r="M17" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N17" s="19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -3349,29 +3374,29 @@
       <c r="F18" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="32" t="s">
         <v>130</v>
       </c>
       <c r="H18" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="I18" s="19" t="s">
+      <c r="K18" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="J18" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="K18" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L18" s="19" t="s">
+      <c r="N18" s="19" t="s">
         <v>133</v>
-      </c>
-      <c r="M18" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N18" s="19" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:14">
@@ -3530,7 +3555,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:U55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12.6181818181818" customWidth="1"/>
@@ -3568,7 +3593,7 @@
         <v>152</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>153</v>
@@ -3616,60 +3641,69 @@
         <v>167</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="str">
-        <f>VLOOKUP(C2,$C$40:$D$56,2,0)</f>
-        <v>002183</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>14</v>
+      <c r="B2" s="20" t="str">
+        <f>VLOOKUP(C2,$C$39:$D$55,2,0)</f>
+        <v>005693</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>26</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="24">
-        <v>81070.62</v>
-      </c>
-      <c r="K2" s="21">
-        <f>J2</f>
-        <v>81070.62</v>
-      </c>
-      <c r="L2" s="21">
-        <v>1064.62</v>
-      </c>
-      <c r="M2" s="25">
-        <f>L2/K2</f>
-        <v>0.0131320076249571</v>
-      </c>
-      <c r="N2" s="26">
-        <v>0</v>
+      <c r="F2" s="22">
+        <v>399.82</v>
+      </c>
+      <c r="G2" s="23">
+        <v>1.4256</v>
+      </c>
+      <c r="H2" s="22">
+        <f t="shared" ref="H2:H17" si="0">F2*0.2</f>
+        <v>79.964</v>
+      </c>
+      <c r="I2" s="24">
+        <v>1.4484</v>
+      </c>
+      <c r="J2" s="25">
+        <f t="shared" ref="J2:J17" si="1">I2*F2</f>
+        <v>579.099288</v>
+      </c>
+      <c r="K2" s="22">
+        <f t="shared" ref="K2:K17" si="2">F2*G2</f>
+        <v>569.983392</v>
+      </c>
+      <c r="L2" s="22">
+        <f t="shared" ref="L2:L17" si="3">J2-K2</f>
+        <v>9.11589600000002</v>
+      </c>
+      <c r="M2" s="26">
+        <f t="shared" ref="M2:M17" si="4">L2/K2</f>
+        <v>0.015993265993266</v>
+      </c>
+      <c r="N2" s="27">
+        <v>1</v>
       </c>
       <c r="O2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="19" t="s">
-        <v>17</v>
+        <v>169</v>
+      </c>
+      <c r="P2" s="19">
+        <v>100</v>
       </c>
       <c r="Q2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R2" s="19" t="s">
-        <v>17</v>
+        <v>170</v>
+      </c>
+      <c r="R2" s="19">
+        <v>270</v>
       </c>
       <c r="S2" s="19" t="s">
         <v>17</v>
@@ -3685,62 +3719,62 @@
       <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="27" t="str">
-        <f>VLOOKUP(C3,$C$40:$D$56,2,0)</f>
-        <v>005693</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>26</v>
+      <c r="B3" s="19" t="str">
+        <f t="shared" ref="B3:B11" si="5">VLOOKUP(C3,$C$39:$D$55,2,0)</f>
+        <v>008702</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>38</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E3" s="20">
+        <v>168</v>
+      </c>
+      <c r="E3" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F3" s="21">
-        <v>399.82</v>
-      </c>
-      <c r="G3" s="22">
-        <v>1.4256</v>
-      </c>
-      <c r="H3" s="21">
-        <f t="shared" ref="H3:H18" si="0">F3*0.2</f>
-        <v>79.964</v>
-      </c>
-      <c r="I3" s="23">
-        <v>1.4484</v>
-      </c>
-      <c r="J3" s="24">
-        <f t="shared" ref="J3:J18" si="1">I3*F3</f>
-        <v>579.099288</v>
-      </c>
-      <c r="K3" s="21">
-        <f t="shared" ref="K3:K18" si="2">F3*G3</f>
-        <v>569.983392</v>
-      </c>
-      <c r="L3" s="21">
-        <f t="shared" ref="L3:L18" si="3">J3-K3</f>
-        <v>9.11589600000002</v>
-      </c>
-      <c r="M3" s="25">
-        <f t="shared" ref="M3:M18" si="4">L3/K3</f>
-        <v>0.015993265993266</v>
-      </c>
-      <c r="N3" s="26">
+      <c r="F3" s="22">
+        <v>479.56</v>
+      </c>
+      <c r="G3" s="23">
+        <v>2.5023</v>
+      </c>
+      <c r="H3" s="22">
+        <f t="shared" si="0"/>
+        <v>95.912</v>
+      </c>
+      <c r="I3" s="24">
+        <v>2.4685</v>
+      </c>
+      <c r="J3" s="25">
+        <f t="shared" si="1"/>
+        <v>1183.79386</v>
+      </c>
+      <c r="K3" s="22">
+        <f t="shared" si="2"/>
+        <v>1200.002988</v>
+      </c>
+      <c r="L3" s="22">
+        <f t="shared" si="3"/>
+        <v>-16.209128</v>
+      </c>
+      <c r="M3" s="26">
+        <f t="shared" si="4"/>
+        <v>-0.0135075730328098</v>
+      </c>
+      <c r="N3" s="27">
         <v>1</v>
       </c>
       <c r="O3" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="P3" s="19">
+        <v>200</v>
+      </c>
+      <c r="Q3" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="P3" s="19">
-        <v>100</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>171</v>
-      </c>
       <c r="R3" s="19">
-        <v>270</v>
+        <v>2000</v>
       </c>
       <c r="S3" s="19" t="s">
         <v>17</v>
@@ -3757,48 +3791,48 @@
         <v>3</v>
       </c>
       <c r="B4" s="19" t="str">
-        <f t="shared" ref="B4:B12" si="5">VLOOKUP(C4,$C$40:$D$56,2,0)</f>
-        <v>008702</v>
+        <f t="shared" si="5"/>
+        <v>009034</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="20">
+        <v>168</v>
+      </c>
+      <c r="E4" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F4" s="21">
-        <v>479.56</v>
-      </c>
-      <c r="G4" s="22">
-        <v>2.5023</v>
-      </c>
-      <c r="H4" s="21">
+      <c r="F4" s="22">
+        <v>383.5</v>
+      </c>
+      <c r="G4" s="23">
+        <v>2.556</v>
+      </c>
+      <c r="H4" s="22">
         <f t="shared" si="0"/>
-        <v>95.912</v>
-      </c>
-      <c r="I4" s="23">
-        <v>2.4685</v>
-      </c>
-      <c r="J4" s="24">
+        <v>76.7</v>
+      </c>
+      <c r="I4" s="24">
+        <v>2.636</v>
+      </c>
+      <c r="J4" s="25">
         <f t="shared" si="1"/>
-        <v>1183.79386</v>
-      </c>
-      <c r="K4" s="21">
+        <v>1010.906</v>
+      </c>
+      <c r="K4" s="22">
         <f t="shared" si="2"/>
-        <v>1200.002988</v>
-      </c>
-      <c r="L4" s="21">
+        <v>980.226</v>
+      </c>
+      <c r="L4" s="22">
         <f t="shared" si="3"/>
-        <v>-16.209128</v>
-      </c>
-      <c r="M4" s="25">
+        <v>30.6800000000001</v>
+      </c>
+      <c r="M4" s="26">
         <f t="shared" si="4"/>
-        <v>-0.0135075730328098</v>
-      </c>
-      <c r="N4" s="26">
+        <v>0.0312989045383412</v>
+      </c>
+      <c r="N4" s="27">
         <v>1</v>
       </c>
       <c r="O4" s="19" t="s">
@@ -3808,10 +3842,10 @@
         <v>200</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R4" s="19">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="S4" s="19" t="s">
         <v>17</v>
@@ -3829,47 +3863,47 @@
       </c>
       <c r="B5" s="19" t="str">
         <f t="shared" si="5"/>
-        <v>009034</v>
+        <v>009505</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" s="20">
+        <v>168</v>
+      </c>
+      <c r="E5" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F5" s="21">
-        <v>383.5</v>
-      </c>
-      <c r="G5" s="22">
-        <v>2.556</v>
-      </c>
-      <c r="H5" s="21">
+      <c r="F5" s="22">
+        <v>416.65</v>
+      </c>
+      <c r="G5" s="23">
+        <v>2.4001</v>
+      </c>
+      <c r="H5" s="22">
         <f t="shared" si="0"/>
-        <v>76.7</v>
-      </c>
-      <c r="I5" s="23">
-        <v>2.636</v>
-      </c>
-      <c r="J5" s="24">
+        <v>83.33</v>
+      </c>
+      <c r="I5" s="24">
+        <v>2.3958</v>
+      </c>
+      <c r="J5" s="25">
         <f t="shared" si="1"/>
-        <v>1010.906</v>
-      </c>
-      <c r="K5" s="21">
+        <v>998.21007</v>
+      </c>
+      <c r="K5" s="22">
         <f t="shared" si="2"/>
-        <v>980.226</v>
-      </c>
-      <c r="L5" s="21">
+        <v>1000.001665</v>
+      </c>
+      <c r="L5" s="22">
         <f t="shared" si="3"/>
-        <v>30.6800000000001</v>
-      </c>
-      <c r="M5" s="25">
+        <v>-1.79159500000014</v>
+      </c>
+      <c r="M5" s="26">
         <f t="shared" si="4"/>
-        <v>0.0312989045383412</v>
-      </c>
-      <c r="N5" s="26">
+        <v>-0.00179159201699943</v>
+      </c>
+      <c r="N5" s="27">
         <v>1</v>
       </c>
       <c r="O5" s="19" t="s">
@@ -3879,10 +3913,10 @@
         <v>200</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R5" s="19">
-        <v>2200</v>
+        <v>2800</v>
       </c>
       <c r="S5" s="19" t="s">
         <v>17</v>
@@ -3900,47 +3934,47 @@
       </c>
       <c r="B6" s="19" t="str">
         <f t="shared" si="5"/>
-        <v>009505</v>
+        <v>014662</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" s="20">
+        <v>168</v>
+      </c>
+      <c r="E6" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F6" s="21">
-        <v>416.65</v>
-      </c>
-      <c r="G6" s="22">
-        <v>2.4001</v>
-      </c>
-      <c r="H6" s="21">
+      <c r="F6" s="22">
+        <v>233.16</v>
+      </c>
+      <c r="G6" s="23">
+        <v>2.5733</v>
+      </c>
+      <c r="H6" s="22">
         <f t="shared" si="0"/>
-        <v>83.33</v>
-      </c>
-      <c r="I6" s="23">
-        <v>2.3958</v>
-      </c>
-      <c r="J6" s="24">
+        <v>46.632</v>
+      </c>
+      <c r="I6" s="24">
+        <v>2.5423</v>
+      </c>
+      <c r="J6" s="25">
         <f t="shared" si="1"/>
-        <v>998.21007</v>
-      </c>
-      <c r="K6" s="21">
+        <v>592.762668</v>
+      </c>
+      <c r="K6" s="22">
         <f t="shared" si="2"/>
-        <v>1000.001665</v>
-      </c>
-      <c r="L6" s="21">
+        <v>599.990628</v>
+      </c>
+      <c r="L6" s="22">
         <f t="shared" si="3"/>
-        <v>-1.79159500000014</v>
-      </c>
-      <c r="M6" s="25">
+        <v>-7.22796000000005</v>
+      </c>
+      <c r="M6" s="26">
         <f t="shared" si="4"/>
-        <v>-0.00179159201699943</v>
-      </c>
-      <c r="N6" s="26">
+        <v>-0.0120467881708313</v>
+      </c>
+      <c r="N6" s="27">
         <v>1</v>
       </c>
       <c r="O6" s="19" t="s">
@@ -3950,10 +3984,10 @@
         <v>200</v>
       </c>
       <c r="Q6" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R6" s="19">
-        <v>2800</v>
+        <v>5500</v>
       </c>
       <c r="S6" s="19" t="s">
         <v>17</v>
@@ -3969,62 +4003,62 @@
       <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="str">
+      <c r="B7" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>014662</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>61</v>
+        <v>014881</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>67</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E7" s="20">
+        <v>168</v>
+      </c>
+      <c r="E7" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F7" s="21">
-        <v>233.16</v>
-      </c>
-      <c r="G7" s="22">
-        <v>2.5733</v>
-      </c>
-      <c r="H7" s="21">
+      <c r="F7" s="22">
+        <v>1572.57</v>
+      </c>
+      <c r="G7" s="23">
+        <v>1.2718</v>
+      </c>
+      <c r="H7" s="22">
         <f t="shared" si="0"/>
-        <v>46.632</v>
-      </c>
-      <c r="I7" s="23">
-        <v>2.5423</v>
-      </c>
-      <c r="J7" s="24">
+        <v>314.514</v>
+      </c>
+      <c r="I7" s="24">
+        <v>1.2077</v>
+      </c>
+      <c r="J7" s="25">
         <f t="shared" si="1"/>
-        <v>592.762668</v>
-      </c>
-      <c r="K7" s="21">
+        <v>1899.192789</v>
+      </c>
+      <c r="K7" s="22">
         <f t="shared" si="2"/>
-        <v>599.990628</v>
-      </c>
-      <c r="L7" s="21">
+        <v>1999.994526</v>
+      </c>
+      <c r="L7" s="22">
         <f t="shared" si="3"/>
-        <v>-7.22796000000005</v>
-      </c>
-      <c r="M7" s="25">
+        <v>-100.801737</v>
+      </c>
+      <c r="M7" s="26">
         <f t="shared" si="4"/>
-        <v>-0.0120467881708313</v>
-      </c>
-      <c r="N7" s="26">
-        <v>1</v>
+        <v>-0.0504010064475547</v>
+      </c>
+      <c r="N7" s="27">
+        <v>0</v>
       </c>
       <c r="O7" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="P7" s="19">
-        <v>200</v>
+        <v>17</v>
+      </c>
+      <c r="P7" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="Q7" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="R7" s="19">
-        <v>5500</v>
+        <v>17</v>
+      </c>
+      <c r="R7" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="S7" s="19" t="s">
         <v>17</v>
@@ -4040,62 +4074,62 @@
       <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="27" t="str">
+      <c r="B8" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>014881</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>67</v>
+        <v>017470</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>75</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E8" s="20">
+        <v>168</v>
+      </c>
+      <c r="E8" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F8" s="21">
-        <v>1572.57</v>
-      </c>
-      <c r="G8" s="22">
-        <v>1.2718</v>
-      </c>
-      <c r="H8" s="21">
+      <c r="F8" s="22">
+        <v>433.92</v>
+      </c>
+      <c r="G8" s="23">
+        <v>2.1663</v>
+      </c>
+      <c r="H8" s="22">
         <f t="shared" si="0"/>
-        <v>314.514</v>
-      </c>
-      <c r="I8" s="23">
-        <v>1.2077</v>
-      </c>
-      <c r="J8" s="24">
+        <v>86.784</v>
+      </c>
+      <c r="I8" s="24">
+        <v>2.1024</v>
+      </c>
+      <c r="J8" s="25">
         <f t="shared" si="1"/>
-        <v>1899.192789</v>
-      </c>
-      <c r="K8" s="21">
+        <v>912.273408</v>
+      </c>
+      <c r="K8" s="22">
         <f t="shared" si="2"/>
-        <v>1999.994526</v>
-      </c>
-      <c r="L8" s="21">
+        <v>940.000896</v>
+      </c>
+      <c r="L8" s="22">
         <f t="shared" si="3"/>
-        <v>-100.801737</v>
-      </c>
-      <c r="M8" s="25">
+        <v>-27.7274880000002</v>
+      </c>
+      <c r="M8" s="26">
         <f t="shared" si="4"/>
-        <v>-0.0504010064475547</v>
-      </c>
-      <c r="N8" s="26">
-        <v>0</v>
+        <v>-0.0294972995429998</v>
+      </c>
+      <c r="N8" s="27">
+        <v>1</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P8" s="19" t="s">
-        <v>17</v>
+        <v>175</v>
+      </c>
+      <c r="P8" s="19">
+        <v>100</v>
       </c>
       <c r="Q8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R8" s="19" t="s">
-        <v>17</v>
+        <v>176</v>
+      </c>
+      <c r="R8" s="19">
+        <v>840</v>
       </c>
       <c r="S8" s="19" t="s">
         <v>17</v>
@@ -4111,62 +4145,62 @@
       <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="27" t="str">
+      <c r="B9" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>017470</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>75</v>
+        <v>018345</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>83</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E9" s="20">
+        <v>168</v>
+      </c>
+      <c r="E9" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F9" s="21">
-        <v>433.92</v>
-      </c>
-      <c r="G9" s="22">
-        <v>2.1663</v>
-      </c>
-      <c r="H9" s="21">
+      <c r="F9" s="22">
+        <v>1545.12</v>
+      </c>
+      <c r="G9" s="23">
+        <v>1.2944</v>
+      </c>
+      <c r="H9" s="22">
         <f t="shared" si="0"/>
-        <v>86.784</v>
-      </c>
-      <c r="I9" s="23">
-        <v>2.1024</v>
-      </c>
-      <c r="J9" s="24">
+        <v>309.024</v>
+      </c>
+      <c r="I9" s="24">
+        <v>1.2294</v>
+      </c>
+      <c r="J9" s="25">
         <f t="shared" si="1"/>
-        <v>912.273408</v>
-      </c>
-      <c r="K9" s="21">
+        <v>1899.570528</v>
+      </c>
+      <c r="K9" s="22">
         <f t="shared" si="2"/>
-        <v>940.000896</v>
-      </c>
-      <c r="L9" s="21">
+        <v>2000.003328</v>
+      </c>
+      <c r="L9" s="22">
         <f t="shared" si="3"/>
-        <v>-27.7274880000002</v>
-      </c>
-      <c r="M9" s="25">
+        <v>-100.4328</v>
+      </c>
+      <c r="M9" s="26">
         <f t="shared" si="4"/>
-        <v>-0.0294972995429998</v>
-      </c>
-      <c r="N9" s="26">
-        <v>1</v>
+        <v>-0.0502163164400494</v>
+      </c>
+      <c r="N9" s="27">
+        <v>0</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="P9" s="19">
-        <v>100</v>
+        <v>17</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="R9" s="19">
-        <v>840</v>
+        <v>17</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="S9" s="19" t="s">
         <v>17</v>
@@ -4182,62 +4216,62 @@
       <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="27" t="str">
+      <c r="B10" s="19" t="str">
         <f t="shared" si="5"/>
-        <v>018345</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>83</v>
+        <v>020341</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" s="20">
+        <v>168</v>
+      </c>
+      <c r="E10" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F10" s="21">
-        <v>1545.12</v>
-      </c>
-      <c r="G10" s="22">
-        <v>1.2944</v>
-      </c>
-      <c r="H10" s="21">
+      <c r="F10" s="22">
+        <v>388.55</v>
+      </c>
+      <c r="G10" s="23">
+        <v>2.5737</v>
+      </c>
+      <c r="H10" s="22">
         <f t="shared" si="0"/>
-        <v>309.024</v>
-      </c>
-      <c r="I10" s="23">
-        <v>1.2294</v>
-      </c>
-      <c r="J10" s="24">
+        <v>77.71</v>
+      </c>
+      <c r="I10" s="24">
+        <v>2.5857</v>
+      </c>
+      <c r="J10" s="25">
         <f t="shared" si="1"/>
-        <v>1899.570528</v>
-      </c>
-      <c r="K10" s="21">
+        <v>1004.673735</v>
+      </c>
+      <c r="K10" s="22">
         <f t="shared" si="2"/>
-        <v>2000.003328</v>
-      </c>
-      <c r="L10" s="21">
+        <v>1000.011135</v>
+      </c>
+      <c r="L10" s="22">
         <f t="shared" si="3"/>
-        <v>-100.4328</v>
-      </c>
-      <c r="M10" s="25">
+        <v>4.6626</v>
+      </c>
+      <c r="M10" s="26">
         <f t="shared" si="4"/>
-        <v>-0.0502163164400494</v>
-      </c>
-      <c r="N10" s="26">
-        <v>0</v>
+        <v>0.0046625480825271</v>
+      </c>
+      <c r="N10" s="27">
+        <v>1</v>
       </c>
       <c r="O10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P10" s="19" t="s">
-        <v>17</v>
+        <v>177</v>
+      </c>
+      <c r="P10" s="19">
+        <v>200</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R10" s="19" t="s">
-        <v>17</v>
+        <v>170</v>
+      </c>
+      <c r="R10" s="19">
+        <v>2000</v>
       </c>
       <c r="S10" s="19" t="s">
         <v>17</v>
@@ -4253,62 +4287,62 @@
       <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="str">
+      <c r="B11" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>020341</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>87</v>
+        <v>020482</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E11" s="20">
+        <v>168</v>
+      </c>
+      <c r="E11" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F11" s="21">
-        <v>388.55</v>
-      </c>
-      <c r="G11" s="22">
-        <v>2.5737</v>
-      </c>
-      <c r="H11" s="21">
+      <c r="F11" s="22">
+        <v>1209.85</v>
+      </c>
+      <c r="G11" s="23">
+        <v>1.6531</v>
+      </c>
+      <c r="H11" s="22">
         <f t="shared" si="0"/>
-        <v>77.71</v>
-      </c>
-      <c r="I11" s="23">
-        <v>2.5857</v>
-      </c>
-      <c r="J11" s="24">
+        <v>241.97</v>
+      </c>
+      <c r="I11" s="24">
+        <v>1.57</v>
+      </c>
+      <c r="J11" s="25">
         <f t="shared" si="1"/>
-        <v>1004.673735</v>
-      </c>
-      <c r="K11" s="21">
+        <v>1899.4645</v>
+      </c>
+      <c r="K11" s="22">
         <f t="shared" si="2"/>
-        <v>1000.011135</v>
-      </c>
-      <c r="L11" s="21">
+        <v>2000.003035</v>
+      </c>
+      <c r="L11" s="22">
         <f t="shared" si="3"/>
-        <v>4.6626</v>
-      </c>
-      <c r="M11" s="25">
+        <v>-100.538535</v>
+      </c>
+      <c r="M11" s="26">
         <f t="shared" si="4"/>
-        <v>0.0046625480825271</v>
-      </c>
-      <c r="N11" s="26">
-        <v>1</v>
+        <v>-0.0502691912165023</v>
+      </c>
+      <c r="N11" s="27">
+        <v>0</v>
       </c>
       <c r="O11" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="P11" s="19">
-        <v>200</v>
+        <v>17</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="Q11" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="R11" s="19">
-        <v>2000</v>
+        <v>17</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="S11" s="19" t="s">
         <v>17</v>
@@ -4324,49 +4358,48 @@
       <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="27" t="str">
-        <f t="shared" si="5"/>
-        <v>020482</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>93</v>
+      <c r="B12" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>99</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12" s="20">
+        <v>178</v>
+      </c>
+      <c r="E12" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F12" s="21">
-        <v>1209.85</v>
-      </c>
-      <c r="G12" s="22">
-        <v>1.6531</v>
-      </c>
-      <c r="H12" s="21">
+      <c r="F12" s="22">
+        <v>600</v>
+      </c>
+      <c r="G12" s="23">
+        <v>1.506</v>
+      </c>
+      <c r="H12" s="22">
         <f t="shared" si="0"/>
-        <v>241.97</v>
-      </c>
-      <c r="I12" s="23">
-        <v>1.57</v>
-      </c>
-      <c r="J12" s="24">
+        <v>120</v>
+      </c>
+      <c r="I12" s="24">
+        <v>1.498</v>
+      </c>
+      <c r="J12" s="25">
         <f t="shared" si="1"/>
-        <v>1899.4645</v>
-      </c>
-      <c r="K12" s="21">
+        <v>898.8</v>
+      </c>
+      <c r="K12" s="22">
         <f t="shared" si="2"/>
-        <v>2000.003035</v>
-      </c>
-      <c r="L12" s="21">
+        <v>903.6</v>
+      </c>
+      <c r="L12" s="22">
         <f t="shared" si="3"/>
-        <v>-100.538535</v>
-      </c>
-      <c r="M12" s="25">
+        <v>-4.80000000000007</v>
+      </c>
+      <c r="M12" s="26">
         <f t="shared" si="4"/>
-        <v>-0.0502691912165023</v>
-      </c>
-      <c r="N12" s="26">
+        <v>-0.00531208499335997</v>
+      </c>
+      <c r="N12" s="27">
         <v>0</v>
       </c>
       <c r="O12" s="19" t="s">
@@ -4395,48 +4428,48 @@
       <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>99</v>
+      <c r="B13" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>106</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E13" s="20">
+        <v>178</v>
+      </c>
+      <c r="E13" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="22">
         <v>600</v>
       </c>
-      <c r="G13" s="22">
-        <v>1.506</v>
-      </c>
-      <c r="H13" s="21">
+      <c r="G13" s="23">
+        <v>1.538</v>
+      </c>
+      <c r="H13" s="22">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="I13" s="23">
-        <v>1.498</v>
-      </c>
-      <c r="J13" s="24">
+      <c r="I13" s="24">
+        <v>1.528</v>
+      </c>
+      <c r="J13" s="25">
         <f t="shared" si="1"/>
-        <v>898.8</v>
-      </c>
-      <c r="K13" s="21">
+        <v>916.8</v>
+      </c>
+      <c r="K13" s="22">
         <f t="shared" si="2"/>
-        <v>903.6</v>
-      </c>
-      <c r="L13" s="21">
+        <v>922.8</v>
+      </c>
+      <c r="L13" s="22">
         <f t="shared" si="3"/>
-        <v>-4.80000000000007</v>
-      </c>
-      <c r="M13" s="25">
+        <v>-6</v>
+      </c>
+      <c r="M13" s="26">
         <f t="shared" si="4"/>
-        <v>-0.00531208499335997</v>
-      </c>
-      <c r="N13" s="26">
+        <v>-0.00650195058517555</v>
+      </c>
+      <c r="N13" s="27">
         <v>0</v>
       </c>
       <c r="O13" s="19" t="s">
@@ -4465,48 +4498,48 @@
       <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>106</v>
+      <c r="B14" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>109</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="20">
+        <v>178</v>
+      </c>
+      <c r="E14" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F14" s="21">
-        <v>600</v>
-      </c>
-      <c r="G14" s="22">
-        <v>1.538</v>
-      </c>
-      <c r="H14" s="21">
+      <c r="F14" s="22">
+        <v>1500</v>
+      </c>
+      <c r="G14" s="23">
+        <v>1.609</v>
+      </c>
+      <c r="H14" s="22">
         <f t="shared" si="0"/>
-        <v>120</v>
-      </c>
-      <c r="I14" s="23">
-        <v>1.528</v>
-      </c>
-      <c r="J14" s="24">
+        <v>300</v>
+      </c>
+      <c r="I14" s="24">
+        <v>1.48</v>
+      </c>
+      <c r="J14" s="25">
         <f t="shared" si="1"/>
-        <v>916.8</v>
-      </c>
-      <c r="K14" s="21">
+        <v>2220</v>
+      </c>
+      <c r="K14" s="22">
         <f t="shared" si="2"/>
-        <v>922.8</v>
-      </c>
-      <c r="L14" s="21">
+        <v>2413.5</v>
+      </c>
+      <c r="L14" s="22">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="M14" s="25">
+        <v>-193.5</v>
+      </c>
+      <c r="M14" s="26">
         <f t="shared" si="4"/>
-        <v>-0.00650195058517555</v>
-      </c>
-      <c r="N14" s="26">
+        <v>-0.0801740211311373</v>
+      </c>
+      <c r="N14" s="27">
         <v>0</v>
       </c>
       <c r="O14" s="19" t="s">
@@ -4535,48 +4568,48 @@
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>109</v>
+      <c r="B15" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>116</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E15" s="20">
+        <v>178</v>
+      </c>
+      <c r="E15" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F15" s="21">
-        <v>1500</v>
-      </c>
-      <c r="G15" s="22">
-        <v>1.609</v>
-      </c>
-      <c r="H15" s="21">
+      <c r="F15" s="22">
+        <v>1600</v>
+      </c>
+      <c r="G15" s="23">
+        <v>1.123</v>
+      </c>
+      <c r="H15" s="22">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="I15" s="23">
-        <v>1.48</v>
-      </c>
-      <c r="J15" s="24">
+        <v>320</v>
+      </c>
+      <c r="I15" s="24">
+        <v>1.061</v>
+      </c>
+      <c r="J15" s="25">
         <f t="shared" si="1"/>
-        <v>2220</v>
-      </c>
-      <c r="K15" s="21">
+        <v>1697.6</v>
+      </c>
+      <c r="K15" s="22">
         <f t="shared" si="2"/>
-        <v>2413.5</v>
-      </c>
-      <c r="L15" s="21">
+        <v>1796.8</v>
+      </c>
+      <c r="L15" s="22">
         <f t="shared" si="3"/>
-        <v>-193.5</v>
-      </c>
-      <c r="M15" s="25">
+        <v>-99.2</v>
+      </c>
+      <c r="M15" s="26">
         <f t="shared" si="4"/>
-        <v>-0.0801740211311373</v>
-      </c>
-      <c r="N15" s="26">
+        <v>-0.0552092609082814</v>
+      </c>
+      <c r="N15" s="27">
         <v>0</v>
       </c>
       <c r="O15" s="19" t="s">
@@ -4605,48 +4638,48 @@
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>116</v>
+      <c r="B16" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>121</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E16" s="20">
+        <v>178</v>
+      </c>
+      <c r="E16" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F16" s="21">
-        <v>1600</v>
-      </c>
-      <c r="G16" s="22">
-        <v>1.123</v>
-      </c>
-      <c r="H16" s="21">
+      <c r="F16" s="22">
+        <v>1500</v>
+      </c>
+      <c r="G16" s="23">
+        <v>0.938</v>
+      </c>
+      <c r="H16" s="22">
         <f t="shared" si="0"/>
-        <v>320</v>
-      </c>
-      <c r="I16" s="23">
-        <v>1.061</v>
-      </c>
-      <c r="J16" s="24">
+        <v>300</v>
+      </c>
+      <c r="I16" s="24">
+        <v>0.92</v>
+      </c>
+      <c r="J16" s="25">
         <f t="shared" si="1"/>
-        <v>1697.6</v>
-      </c>
-      <c r="K16" s="21">
+        <v>1380</v>
+      </c>
+      <c r="K16" s="22">
         <f t="shared" si="2"/>
-        <v>1796.8</v>
-      </c>
-      <c r="L16" s="21">
+        <v>1407</v>
+      </c>
+      <c r="L16" s="22">
         <f t="shared" si="3"/>
-        <v>-99.2</v>
-      </c>
-      <c r="M16" s="25">
+        <v>-27</v>
+      </c>
+      <c r="M16" s="26">
         <f t="shared" si="4"/>
-        <v>-0.0552092609082814</v>
-      </c>
-      <c r="N16" s="26">
+        <v>-0.0191897654584222</v>
+      </c>
+      <c r="N16" s="27">
         <v>0</v>
       </c>
       <c r="O16" s="19" t="s">
@@ -4675,48 +4708,48 @@
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>121</v>
+      <c r="B17" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>128</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E17" s="20">
+        <v>178</v>
+      </c>
+      <c r="E17" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F17" s="21">
-        <v>1500</v>
-      </c>
-      <c r="G17" s="22">
-        <v>0.938</v>
-      </c>
-      <c r="H17" s="21">
+      <c r="F17" s="22">
+        <v>200</v>
+      </c>
+      <c r="G17" s="23">
+        <v>0.786</v>
+      </c>
+      <c r="H17" s="22">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="I17" s="23">
-        <v>0.92</v>
-      </c>
-      <c r="J17" s="24">
+        <v>40</v>
+      </c>
+      <c r="I17" s="24">
+        <v>0.737</v>
+      </c>
+      <c r="J17" s="25">
         <f t="shared" si="1"/>
-        <v>1380</v>
-      </c>
-      <c r="K17" s="21">
+        <v>147.4</v>
+      </c>
+      <c r="K17" s="22">
         <f t="shared" si="2"/>
-        <v>1407</v>
-      </c>
-      <c r="L17" s="21">
+        <v>157.2</v>
+      </c>
+      <c r="L17" s="22">
         <f t="shared" si="3"/>
-        <v>-27</v>
-      </c>
-      <c r="M17" s="25">
+        <v>-9.80000000000001</v>
+      </c>
+      <c r="M17" s="26">
         <f t="shared" si="4"/>
-        <v>-0.0191897654584222</v>
-      </c>
-      <c r="N17" s="26">
+        <v>-0.0623409669211197</v>
+      </c>
+      <c r="N17" s="27">
         <v>0</v>
       </c>
       <c r="O17" s="19" t="s">
@@ -4745,298 +4778,304 @@
       <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>128</v>
+      <c r="C18" t="s">
+        <v>179</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E18" s="20">
+        <v>178</v>
+      </c>
+      <c r="E18" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F18" s="21">
-        <v>200</v>
-      </c>
-      <c r="G18" s="22">
-        <v>0.786</v>
-      </c>
-      <c r="H18" s="21">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="I18" s="23">
-        <v>0.737</v>
-      </c>
-      <c r="J18" s="24">
-        <f t="shared" si="1"/>
-        <v>147.4</v>
-      </c>
-      <c r="K18" s="21">
-        <f t="shared" si="2"/>
-        <v>157.2</v>
-      </c>
-      <c r="L18" s="21">
-        <f t="shared" si="3"/>
-        <v>-9.80000000000001</v>
-      </c>
-      <c r="M18" s="25">
-        <f t="shared" si="4"/>
-        <v>-0.0623409669211197</v>
-      </c>
-      <c r="N18" s="26">
+      <c r="J18" s="11">
+        <v>23000</v>
+      </c>
+      <c r="K18" s="8">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" s="1"/>
+      <c r="B19" s="19" t="str">
+        <f>VLOOKUP(C19,$C$39:$D$55,2,0)</f>
+        <v>002183</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E19" s="21">
+        <v>46088.9471296296</v>
+      </c>
+      <c r="F19" s="22"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="25">
+        <v>81070.62</v>
+      </c>
+      <c r="K19" s="22">
+        <f>J19</f>
+        <v>81070.62</v>
+      </c>
+      <c r="L19" s="22">
+        <v>1064.62</v>
+      </c>
+      <c r="M19" s="26">
+        <f>L19/K19</f>
+        <v>0.0131320076249571</v>
+      </c>
+      <c r="N19" s="27">
         <v>0</v>
       </c>
-      <c r="O18" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P18" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q18" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R18" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S18" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T18" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U18" s="19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="C19" t="s">
-        <v>179</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E19" s="20">
-        <v>46088.9471296296</v>
-      </c>
-      <c r="J19" s="11">
-        <v>23000</v>
-      </c>
-      <c r="K19" s="8">
-        <v>23000</v>
+      <c r="O19" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="P19" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q19" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="R19" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="S19" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="T19" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="U19" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="C21" s="28" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="C22" s="28" t="s">
-        <v>180</v>
+      <c r="C22" s="29"/>
+      <c r="J22" s="11">
+        <f>SUM(J2:J17)</f>
+        <v>19240.546846</v>
+      </c>
+      <c r="K22" s="11">
+        <f>SUM(K2:K17)</f>
+        <v>19891.117593</v>
+      </c>
+      <c r="L22" s="11">
+        <f>SUM(L2:L17)</f>
+        <v>-650.570747</v>
+      </c>
+      <c r="M22" s="30">
+        <f>L22/K22</f>
+        <v>-0.0327065959948347</v>
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="C23" s="29"/>
+      <c r="C23" s="28" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="C24" s="28" t="s">
-        <v>181</v>
-      </c>
+      <c r="C24" s="29"/>
     </row>
     <row r="25" spans="1:21">
-      <c r="C25" s="29"/>
+      <c r="C25" s="28" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="C26" s="28" t="s">
-        <v>182</v>
-      </c>
+      <c r="C26" s="29"/>
     </row>
     <row r="27" spans="1:21">
-      <c r="C27" s="29"/>
+      <c r="C27" s="5" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="28" spans="1:21">
       <c r="C28" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="C29" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:21">
-      <c r="C30" s="5" t="s">
-        <v>185</v>
-      </c>
+      <c r="C30" s="29"/>
     </row>
     <row r="31" spans="1:21">
-      <c r="C31" s="29"/>
+      <c r="C31" s="28" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="C32" s="28" t="s">
-        <v>186</v>
-      </c>
+      <c r="C32" s="29"/>
     </row>
     <row r="33" spans="3:4">
-      <c r="C33" s="29"/>
+      <c r="C33" s="5" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="34" spans="3:4">
       <c r="C34" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="3:4">
       <c r="C35" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4">
-      <c r="C36" s="5" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="39" ht="28" spans="3:4">
-      <c r="C39" s="1" t="s">
+    <row r="38" ht="28" spans="3:4">
+      <c r="C38" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4">
+      <c r="C39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="3:4">
       <c r="C40" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="3:4">
       <c r="C41" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="3:4">
       <c r="C42" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="3:4">
       <c r="C43" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="3:4">
       <c r="C44" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="3:4">
       <c r="C45" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="3:4">
       <c r="C46" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="3:4">
       <c r="C47" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="3:4">
       <c r="C48" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="3:4">
       <c r="C49" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="3:4">
-      <c r="C50" s="3" t="s">
-        <v>93</v>
+      <c r="C50" s="19" t="s">
+        <v>99</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="3:4">
       <c r="C51" s="19" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="3:4">
       <c r="C52" s="19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="3:4">
       <c r="C53" s="19" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="3:4">
       <c r="C54" s="19" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="3:4">
       <c r="C55" s="19" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="56" spans="3:4">
-      <c r="C56" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56" s="3" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5092,10 +5131,10 @@
         <v>196</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6234,7 +6273,7 @@
         <v>261</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6764,7 +6803,7 @@
         <v>286</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/数据库表导出_v3.xlsx
+++ b/data/数据库表导出_v3.xlsx
@@ -614,6 +614,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>载体</t>
     </r>
     <r>
@@ -655,6 +661,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>操作</t>
     </r>
     <r>
@@ -714,6 +726,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>逻辑</t>
     </r>
     <r>
@@ -767,6 +785,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>载体</t>
     </r>
     <r>
@@ -808,6 +832,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>操作</t>
     </r>
     <r>
@@ -840,6 +870,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>逻辑</t>
     </r>
     <r>
@@ -1041,6 +1077,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>条 1：</t>
     </r>
     <r>
@@ -1109,6 +1151,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>条 2：</t>
     </r>
     <r>
@@ -1177,6 +1225,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>条 3：</t>
     </r>
     <r>
@@ -1245,6 +1299,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>条 4：</t>
     </r>
     <r>
@@ -1313,6 +1373,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF4C4F69"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>你的系统在生成信号时，只要再加一个条件：</t>
     </r>
     <r>
@@ -2141,7 +2207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2184,9 +2250,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2609,7 +2672,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="30" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -2635,767 +2698,767 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="19" t="str">
-        <f>VLOOKUP(B2,$B$24:$C$40,2,0)</f>
+      <c r="A2" s="2" t="str">
+        <f t="shared" ref="A2:A18" si="0">VLOOKUP(B2,$B$24:$C$40,2,0)</f>
         <v>002183</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="19" t="s">
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="19" t="s">
+      <c r="L2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="19" t="str">
-        <f>VLOOKUP(B3,$B$24:$C$40,2,0)</f>
+      <c r="A3" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>005693</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="19" t="s">
+      <c r="L3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="N3" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="19" t="str">
-        <f>VLOOKUP(B4,$B$24:$C$40,2,0)</f>
+      <c r="A4" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>008702</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="19" t="s">
+      <c r="M4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="19" t="s">
+      <c r="N4" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="19" t="str">
-        <f>VLOOKUP(B5,$B$24:$C$40,2,0)</f>
+      <c r="A5" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>009034</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" s="19" t="s">
+      <c r="L5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="19" t="str">
-        <f>VLOOKUP(B6,$B$24:$C$40,2,0)</f>
+      <c r="A6" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>009505</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6" s="19" t="s">
+      <c r="L6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="19" t="str">
-        <f>VLOOKUP(B7,$B$24:$C$40,2,0)</f>
+      <c r="A7" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>014662</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M7" s="19" t="s">
+      <c r="M7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="N7" s="19" t="s">
+      <c r="N7" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="19" t="str">
-        <f>VLOOKUP(B8,$B$24:$C$40,2,0)</f>
+      <c r="A8" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>014881</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="19" t="s">
+      <c r="N8" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="19" t="str">
-        <f>VLOOKUP(B9,$B$24:$C$40,2,0)</f>
+      <c r="A9" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>017470</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N9" s="19" t="s">
+      <c r="N9" s="2" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="19" t="str">
-        <f>VLOOKUP(B10,$B$24:$C$40,2,0)</f>
+      <c r="A10" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>018345</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="19" t="str">
-        <f>VLOOKUP(B11,$B$24:$C$40,2,0)</f>
+      <c r="A11" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>020341</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="J11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M11" s="19" t="s">
+      <c r="L11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="N11" s="19" t="s">
+      <c r="N11" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="19" t="str">
-        <f>VLOOKUP(B12,$B$24:$C$40,2,0)</f>
+      <c r="A12" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>020482</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J12" s="19" t="s">
+      <c r="J12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="19" t="s">
+      <c r="L12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="N12" s="19" t="s">
+      <c r="N12" s="2" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="19" t="str">
-        <f>VLOOKUP(B13,$B$24:$C$40,2,0)</f>
+      <c r="A13" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>159227</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="19" t="s">
+      <c r="J13" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="K13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" s="19" t="s">
+      <c r="L13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="N13" s="19" t="s">
+      <c r="N13" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="19" t="str">
-        <f>VLOOKUP(B14,$B$24:$C$40,2,0)</f>
+      <c r="A14" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>159241</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J14" s="19" t="s">
+      <c r="J14" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="19" t="s">
+      <c r="L14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="N14" s="19" t="s">
+      <c r="N14" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="19" t="str">
-        <f>VLOOKUP(B15,$B$24:$C$40,2,0)</f>
+      <c r="A15" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>159530</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="I15" s="19" t="s">
+      <c r="I15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L15" s="19" t="s">
+      <c r="L15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="N15" s="19" t="s">
+      <c r="N15" s="2" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="19" t="str">
-        <f>VLOOKUP(B16,$B$24:$C$40,2,0)</f>
+      <c r="A16" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>159770</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="I16" s="19" t="s">
+      <c r="I16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J16" s="19" t="s">
+      <c r="J16" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="K16" s="19" t="s">
+      <c r="K16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L16" s="19" t="s">
+      <c r="L16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M16" s="19" t="s">
+      <c r="M16" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="N16" s="19" t="s">
+      <c r="N16" s="2" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="19" t="str">
-        <f>VLOOKUP(B17,$B$24:$C$40,2,0)</f>
+      <c r="A17" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>159781</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="I17" s="19" t="s">
+      <c r="I17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J17" s="19" t="s">
+      <c r="J17" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K17" s="19" t="s">
+      <c r="K17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L17" s="19" t="s">
+      <c r="L17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M17" s="19" t="s">
+      <c r="M17" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="N17" s="19" t="s">
+      <c r="N17" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="19" t="str">
-        <f>VLOOKUP(B18,$B$24:$C$40,2,0)</f>
+      <c r="A18" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>159792</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I18" s="19" t="s">
+      <c r="I18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J18" s="19" t="s">
+      <c r="J18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L18" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M18" s="19" t="s">
+      <c r="L18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="N18" s="19" t="s">
+      <c r="N18" s="2" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3496,7 +3559,7 @@
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C35" s="3" t="s">
@@ -3504,7 +3567,7 @@
       </c>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -3512,7 +3575,7 @@
       </c>
     </row>
     <row r="37" spans="2:3">
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C37" s="3" t="s">
@@ -3520,7 +3583,7 @@
       </c>
     </row>
     <row r="38" spans="2:3">
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -3528,7 +3591,7 @@
       </c>
     </row>
     <row r="39" spans="2:3">
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -3536,7 +3599,7 @@
       </c>
     </row>
     <row r="40" spans="2:3">
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -3645,1146 +3708,1146 @@
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="19">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="str">
+      <c r="B2" s="19" t="str">
         <f>VLOOKUP(C2,$C$39:$D$55,2,0)</f>
         <v>005693</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="21">
         <v>399.82</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="22">
         <v>1.4256</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="21">
         <f t="shared" ref="H2:H17" si="0">F2*0.2</f>
         <v>79.964</v>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="23">
         <v>1.4484</v>
       </c>
-      <c r="J2" s="25">
+      <c r="J2" s="24">
         <f t="shared" ref="J2:J17" si="1">I2*F2</f>
         <v>579.099288</v>
       </c>
-      <c r="K2" s="22">
+      <c r="K2" s="21">
         <f t="shared" ref="K2:K17" si="2">F2*G2</f>
         <v>569.983392</v>
       </c>
-      <c r="L2" s="22">
+      <c r="L2" s="21">
         <f t="shared" ref="L2:L17" si="3">J2-K2</f>
         <v>9.11589600000002</v>
       </c>
-      <c r="M2" s="26">
+      <c r="M2" s="25">
         <f t="shared" ref="M2:M17" si="4">L2/K2</f>
         <v>0.015993265993266</v>
       </c>
-      <c r="N2" s="27">
+      <c r="N2" s="26">
         <v>1</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="P2" s="19">
+      <c r="P2" s="2">
         <v>100</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="Q2" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="R2" s="19">
+      <c r="R2" s="2">
         <v>270</v>
       </c>
-      <c r="S2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U2" s="19" t="s">
+      <c r="S2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="19">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="str">
+      <c r="B3" s="2" t="str">
         <f t="shared" ref="B3:B11" si="5">VLOOKUP(C3,$C$39:$D$55,2,0)</f>
         <v>008702</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="21">
         <v>479.56</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="22">
         <v>2.5023</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="21">
         <f t="shared" si="0"/>
         <v>95.912</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="23">
         <v>2.4685</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="24">
         <f t="shared" si="1"/>
         <v>1183.79386</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="21">
         <f t="shared" si="2"/>
         <v>1200.002988</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="21">
         <f t="shared" si="3"/>
         <v>-16.209128</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="25">
         <f t="shared" si="4"/>
         <v>-0.0135075730328098</v>
       </c>
-      <c r="N3" s="27">
+      <c r="N3" s="26">
         <v>1</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="O3" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="2">
         <v>200</v>
       </c>
-      <c r="Q3" s="19" t="s">
+      <c r="Q3" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="2">
         <v>2000</v>
       </c>
-      <c r="S3" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T3" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="19" t="s">
+      <c r="S3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="19">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="str">
+      <c r="B4" s="2" t="str">
         <f t="shared" si="5"/>
         <v>009034</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="21">
         <v>383.5</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="22">
         <v>2.556</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="21">
         <f t="shared" si="0"/>
         <v>76.7</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="23">
         <v>2.636</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="24">
         <f t="shared" si="1"/>
         <v>1010.906</v>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="21">
         <f t="shared" si="2"/>
         <v>980.226</v>
       </c>
-      <c r="L4" s="22">
+      <c r="L4" s="21">
         <f t="shared" si="3"/>
         <v>30.6800000000001</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="25">
         <f t="shared" si="4"/>
         <v>0.0312989045383412</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="26">
         <v>1</v>
       </c>
-      <c r="O4" s="19" t="s">
+      <c r="O4" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="P4" s="19">
+      <c r="P4" s="2">
         <v>200</v>
       </c>
-      <c r="Q4" s="19" t="s">
+      <c r="Q4" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="R4" s="19">
+      <c r="R4" s="2">
         <v>2200</v>
       </c>
-      <c r="S4" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T4" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U4" s="19" t="s">
+      <c r="S4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="19">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="str">
+      <c r="B5" s="2" t="str">
         <f t="shared" si="5"/>
         <v>009505</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="21">
         <v>416.65</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="22">
         <v>2.4001</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="21">
         <f t="shared" si="0"/>
         <v>83.33</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="23">
         <v>2.3958</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="24">
         <f t="shared" si="1"/>
         <v>998.21007</v>
       </c>
-      <c r="K5" s="22">
+      <c r="K5" s="21">
         <f t="shared" si="2"/>
         <v>1000.001665</v>
       </c>
-      <c r="L5" s="22">
+      <c r="L5" s="21">
         <f t="shared" si="3"/>
         <v>-1.79159500000014</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="25">
         <f t="shared" si="4"/>
         <v>-0.00179159201699943</v>
       </c>
-      <c r="N5" s="27">
+      <c r="N5" s="26">
         <v>1</v>
       </c>
-      <c r="O5" s="19" t="s">
+      <c r="O5" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="2">
         <v>200</v>
       </c>
-      <c r="Q5" s="19" t="s">
+      <c r="Q5" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="2">
         <v>2800</v>
       </c>
-      <c r="S5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U5" s="19" t="s">
+      <c r="S5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U5" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="19">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="str">
+      <c r="B6" s="2" t="str">
         <f t="shared" si="5"/>
         <v>014662</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="21">
         <v>233.16</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="22">
         <v>2.5733</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="21">
         <f t="shared" si="0"/>
         <v>46.632</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="23">
         <v>2.5423</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="24">
         <f t="shared" si="1"/>
         <v>592.762668</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="21">
         <f t="shared" si="2"/>
         <v>599.990628</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="21">
         <f t="shared" si="3"/>
         <v>-7.22796000000005</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="25">
         <f t="shared" si="4"/>
         <v>-0.0120467881708313</v>
       </c>
-      <c r="N6" s="27">
+      <c r="N6" s="26">
         <v>1</v>
       </c>
-      <c r="O6" s="19" t="s">
+      <c r="O6" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="2">
         <v>200</v>
       </c>
-      <c r="Q6" s="19" t="s">
+      <c r="Q6" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="R6" s="19">
+      <c r="R6" s="2">
         <v>5500</v>
       </c>
-      <c r="S6" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T6" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U6" s="19" t="s">
+      <c r="S6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="19">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="20" t="str">
+      <c r="B7" s="19" t="str">
         <f t="shared" si="5"/>
         <v>014881</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>1572.57</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>1.2718</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <f t="shared" si="0"/>
         <v>314.514</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="23">
         <v>1.2077</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="24">
         <f t="shared" si="1"/>
         <v>1899.192789</v>
       </c>
-      <c r="K7" s="22">
+      <c r="K7" s="21">
         <f t="shared" si="2"/>
         <v>1999.994526</v>
       </c>
-      <c r="L7" s="22">
+      <c r="L7" s="21">
         <f t="shared" si="3"/>
         <v>-100.801737</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="25">
         <f t="shared" si="4"/>
         <v>-0.0504010064475547</v>
       </c>
-      <c r="N7" s="27">
+      <c r="N7" s="26">
         <v>0</v>
       </c>
-      <c r="O7" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P7" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q7" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R7" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S7" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T7" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U7" s="19" t="s">
+      <c r="O7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="19">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="20" t="str">
+      <c r="B8" s="19" t="str">
         <f t="shared" si="5"/>
         <v>017470</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="21">
         <v>433.92</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="22">
         <v>2.1663</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <f t="shared" si="0"/>
         <v>86.784</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="23">
         <v>2.1024</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="24">
         <f t="shared" si="1"/>
         <v>912.273408</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="21">
         <f t="shared" si="2"/>
         <v>940.000896</v>
       </c>
-      <c r="L8" s="22">
+      <c r="L8" s="21">
         <f t="shared" si="3"/>
         <v>-27.7274880000002</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="25">
         <f t="shared" si="4"/>
         <v>-0.0294972995429998</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="26">
         <v>1</v>
       </c>
-      <c r="O8" s="19" t="s">
+      <c r="O8" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="2">
         <v>100</v>
       </c>
-      <c r="Q8" s="19" t="s">
+      <c r="Q8" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="R8" s="19">
+      <c r="R8" s="2">
         <v>840</v>
       </c>
-      <c r="S8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U8" s="19" t="s">
+      <c r="S8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U8" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="19">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="20" t="str">
+      <c r="B9" s="19" t="str">
         <f t="shared" si="5"/>
         <v>018345</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="21">
         <v>1545.12</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="22">
         <v>1.2944</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="21">
         <f t="shared" si="0"/>
         <v>309.024</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="23">
         <v>1.2294</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="24">
         <f t="shared" si="1"/>
         <v>1899.570528</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="21">
         <f t="shared" si="2"/>
         <v>2000.003328</v>
       </c>
-      <c r="L9" s="22">
+      <c r="L9" s="21">
         <f t="shared" si="3"/>
         <v>-100.4328</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="25">
         <f t="shared" si="4"/>
         <v>-0.0502163164400494</v>
       </c>
-      <c r="N9" s="27">
+      <c r="N9" s="26">
         <v>0</v>
       </c>
-      <c r="O9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U9" s="19" t="s">
+      <c r="O9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="19">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B10" s="2" t="str">
         <f t="shared" si="5"/>
         <v>020341</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="21">
         <v>388.55</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="22">
         <v>2.5737</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="21">
         <f t="shared" si="0"/>
         <v>77.71</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="23">
         <v>2.5857</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="24">
         <f t="shared" si="1"/>
         <v>1004.673735</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="21">
         <f t="shared" si="2"/>
         <v>1000.011135</v>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="21">
         <f t="shared" si="3"/>
         <v>4.6626</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="25">
         <f t="shared" si="4"/>
         <v>0.0046625480825271</v>
       </c>
-      <c r="N10" s="27">
+      <c r="N10" s="26">
         <v>1</v>
       </c>
-      <c r="O10" s="19" t="s">
+      <c r="O10" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="2">
         <v>200</v>
       </c>
-      <c r="Q10" s="19" t="s">
+      <c r="Q10" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="R10" s="19">
+      <c r="R10" s="2">
         <v>2000</v>
       </c>
-      <c r="S10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U10" s="19" t="s">
+      <c r="S10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="19">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="20" t="str">
+      <c r="B11" s="19" t="str">
         <f t="shared" si="5"/>
         <v>020482</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="21">
         <v>1209.85</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="22">
         <v>1.6531</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="21">
         <f t="shared" si="0"/>
         <v>241.97</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="23">
         <v>1.57</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="24">
         <f t="shared" si="1"/>
         <v>1899.4645</v>
       </c>
-      <c r="K11" s="22">
+      <c r="K11" s="21">
         <f t="shared" si="2"/>
         <v>2000.003035</v>
       </c>
-      <c r="L11" s="22">
+      <c r="L11" s="21">
         <f t="shared" si="3"/>
         <v>-100.538535</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="25">
         <f t="shared" si="4"/>
         <v>-0.0502691912165023</v>
       </c>
-      <c r="N11" s="27">
+      <c r="N11" s="26">
         <v>0</v>
       </c>
-      <c r="O11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U11" s="19" t="s">
+      <c r="O11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U11" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="19">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="21">
         <v>600</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="22">
         <v>1.506</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="21">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="23">
         <v>1.498</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="24">
         <f t="shared" si="1"/>
         <v>898.8</v>
       </c>
-      <c r="K12" s="22">
+      <c r="K12" s="21">
         <f t="shared" si="2"/>
         <v>903.6</v>
       </c>
-      <c r="L12" s="22">
+      <c r="L12" s="21">
         <f t="shared" si="3"/>
         <v>-4.80000000000007</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="25">
         <f t="shared" si="4"/>
         <v>-0.00531208499335997</v>
       </c>
-      <c r="N12" s="27">
+      <c r="N12" s="26">
         <v>0</v>
       </c>
-      <c r="O12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U12" s="19" t="s">
+      <c r="O12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U12" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="19">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="21">
         <v>600</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="22">
         <v>1.538</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="21">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="23">
         <v>1.528</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="24">
         <f t="shared" si="1"/>
         <v>916.8</v>
       </c>
-      <c r="K13" s="22">
+      <c r="K13" s="21">
         <f t="shared" si="2"/>
         <v>922.8</v>
       </c>
-      <c r="L13" s="22">
+      <c r="L13" s="21">
         <f t="shared" si="3"/>
         <v>-6</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="25">
         <f t="shared" si="4"/>
         <v>-0.00650195058517555</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N13" s="26">
         <v>0</v>
       </c>
-      <c r="O13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U13" s="19" t="s">
+      <c r="O13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U13" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="19">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <v>1500</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="22">
         <v>1.609</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="23">
         <v>1.48</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="24">
         <f t="shared" si="1"/>
         <v>2220</v>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="21">
         <f t="shared" si="2"/>
         <v>2413.5</v>
       </c>
-      <c r="L14" s="22">
+      <c r="L14" s="21">
         <f t="shared" si="3"/>
         <v>-193.5</v>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="25">
         <f t="shared" si="4"/>
         <v>-0.0801740211311373</v>
       </c>
-      <c r="N14" s="27">
+      <c r="N14" s="26">
         <v>0</v>
       </c>
-      <c r="O14" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P14" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q14" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R14" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S14" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T14" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U14" s="19" t="s">
+      <c r="O14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U14" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="19">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="21">
         <v>1600</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="22">
         <v>1.123</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="21">
         <f t="shared" si="0"/>
         <v>320</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="23">
         <v>1.061</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="24">
         <f t="shared" si="1"/>
         <v>1697.6</v>
       </c>
-      <c r="K15" s="22">
+      <c r="K15" s="21">
         <f t="shared" si="2"/>
         <v>1796.8</v>
       </c>
-      <c r="L15" s="22">
+      <c r="L15" s="21">
         <f t="shared" si="3"/>
         <v>-99.2</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="25">
         <f t="shared" si="4"/>
         <v>-0.0552092609082814</v>
       </c>
-      <c r="N15" s="27">
+      <c r="N15" s="26">
         <v>0</v>
       </c>
-      <c r="O15" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P15" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q15" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R15" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S15" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T15" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U15" s="19" t="s">
+      <c r="O15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="19">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <v>1500</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="22">
         <v>0.938</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="23">
         <v>0.92</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="24">
         <f t="shared" si="1"/>
         <v>1380</v>
       </c>
-      <c r="K16" s="22">
+      <c r="K16" s="21">
         <f t="shared" si="2"/>
         <v>1407</v>
       </c>
-      <c r="L16" s="22">
+      <c r="L16" s="21">
         <f t="shared" si="3"/>
         <v>-27</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="25">
         <f t="shared" si="4"/>
         <v>-0.0191897654584222</v>
       </c>
-      <c r="N16" s="27">
+      <c r="N16" s="26">
         <v>0</v>
       </c>
-      <c r="O16" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P16" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q16" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R16" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S16" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T16" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U16" s="19" t="s">
+      <c r="O16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U16" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="19">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="21">
         <v>200</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="22">
         <v>0.786</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="21">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="23">
         <v>0.737</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="24">
         <f t="shared" si="1"/>
         <v>147.4</v>
       </c>
-      <c r="K17" s="22">
+      <c r="K17" s="21">
         <f t="shared" si="2"/>
         <v>157.2</v>
       </c>
-      <c r="L17" s="22">
+      <c r="L17" s="21">
         <f t="shared" si="3"/>
         <v>-9.80000000000001</v>
       </c>
-      <c r="M17" s="26">
+      <c r="M17" s="25">
         <f t="shared" si="4"/>
         <v>-0.0623409669211197</v>
       </c>
-      <c r="N17" s="27">
+      <c r="N17" s="26">
         <v>0</v>
       </c>
-      <c r="O17" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P17" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q17" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R17" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S17" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T17" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U17" s="19" t="s">
+      <c r="O17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U17" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="19">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="C18" t="s">
         <v>179</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <v>46088.9471296296</v>
       </c>
       <c r="J18" s="11">
@@ -4796,71 +4859,71 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="1"/>
-      <c r="B19" s="19" t="str">
+      <c r="B19" s="2" t="str">
         <f>VLOOKUP(C19,$C$39:$D$55,2,0)</f>
         <v>002183</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <v>46088.9471296296</v>
       </c>
-      <c r="F19" s="22"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="25">
+      <c r="F19" s="21"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="24">
         <v>81070.62</v>
       </c>
-      <c r="K19" s="22">
+      <c r="K19" s="21">
         <f>J19</f>
         <v>81070.62</v>
       </c>
-      <c r="L19" s="22">
+      <c r="L19" s="21">
         <v>1064.62</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="25">
         <f>L19/K19</f>
         <v>0.0131320076249571</v>
       </c>
-      <c r="N19" s="27">
+      <c r="N19" s="26">
         <v>0</v>
       </c>
-      <c r="O19" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="P19" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q19" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="R19" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="S19" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="T19" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="U19" s="19" t="s">
+      <c r="O19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U19" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="27" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="C22" s="29"/>
+      <c r="C22" s="28"/>
       <c r="J22" s="11">
         <f>SUM(J2:J17)</f>
         <v>19240.546846</v>
@@ -4873,26 +4936,26 @@
         <f>SUM(L2:L17)</f>
         <v>-650.570747</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="29">
         <f>L22/K22</f>
         <v>-0.0327065959948347</v>
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="27" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="C24" s="29"/>
+      <c r="C24" s="28"/>
     </row>
     <row r="25" spans="1:21">
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="27" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="C26" s="29"/>
+      <c r="C26" s="28"/>
     </row>
     <row r="27" spans="1:21">
       <c r="C27" s="5" t="s">
@@ -4910,15 +4973,15 @@
       </c>
     </row>
     <row r="30" spans="1:21">
-      <c r="C30" s="29"/>
+      <c r="C30" s="28"/>
     </row>
     <row r="31" spans="1:21">
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="27" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="C32" s="29"/>
+      <c r="C32" s="28"/>
     </row>
     <row r="33" spans="3:4">
       <c r="C33" s="5" t="s">
@@ -5032,7 +5095,7 @@
       </c>
     </row>
     <row r="50" spans="3:4">
-      <c r="C50" s="19" t="s">
+      <c r="C50" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -5040,7 +5103,7 @@
       </c>
     </row>
     <row r="51" spans="3:4">
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D51" s="3" t="s">
@@ -5048,7 +5111,7 @@
       </c>
     </row>
     <row r="52" spans="3:4">
-      <c r="C52" s="19" t="s">
+      <c r="C52" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -5056,7 +5119,7 @@
       </c>
     </row>
     <row r="53" spans="3:4">
-      <c r="C53" s="19" t="s">
+      <c r="C53" s="2" t="s">
         <v>116</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -5064,7 +5127,7 @@
       </c>
     </row>
     <row r="54" spans="3:4">
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -5072,7 +5135,7 @@
       </c>
     </row>
     <row r="55" spans="3:4">
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="2" t="s">
         <v>128</v>
       </c>
       <c r="D55" s="3" t="s">

--- a/data/数据库表导出_v3.xlsx
+++ b/data/数据库表导出_v3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080" tabRatio="873" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="12080" tabRatio="873" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="fund_info(基金基本信息表)" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="285">
   <si>
     <t>fund_code
 基金代码</t>
@@ -1432,9 +1432,6 @@
     <t>机器人ETF易方达</t>
   </si>
   <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
     <t>2026-03-06 17:29:31</t>
   </si>
   <si>
@@ -1451,9 +1448,6 @@
   </si>
   <si>
     <t>港股通互联网ETF</t>
-  </si>
-  <si>
-    <t>2026-03-04</t>
   </si>
   <si>
     <t>每天收盘后（15:30 以后）抓取一次最终数据（含最高、最低、收盘）。</t>
@@ -2207,7 +2201,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2216,6 +2210,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2672,7 +2667,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="31" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -2717,7 +2712,7 @@
       <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="32" t="s">
         <v>19</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -2762,7 +2757,7 @@
       <c r="F3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="32" t="s">
         <v>31</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -2807,7 +2802,7 @@
       <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="32" t="s">
         <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -2852,7 +2847,7 @@
       <c r="F5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="32" t="s">
         <v>41</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -2897,7 +2892,7 @@
       <c r="F6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="32" t="s">
         <v>41</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -2942,7 +2937,7 @@
       <c r="F7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="32" t="s">
         <v>41</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -2987,7 +2982,7 @@
       <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -3032,7 +3027,7 @@
       <c r="F9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="32" t="s">
         <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -3077,7 +3072,7 @@
       <c r="F10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -3122,7 +3117,7 @@
       <c r="F11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="32" t="s">
         <v>41</v>
       </c>
       <c r="H11" s="2" t="s">
@@ -3167,7 +3162,7 @@
       <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H12" s="2" t="s">
@@ -3212,7 +3207,7 @@
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="32" t="s">
         <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
@@ -3257,7 +3252,7 @@
       <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="32" t="s">
         <v>102</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -3302,7 +3297,7 @@
       <c r="F15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -3347,7 +3342,7 @@
       <c r="F16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="32" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -3392,7 +3387,7 @@
       <c r="F17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="32" t="s">
         <v>123</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -3437,7 +3432,7 @@
       <c r="F18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="32" t="s">
         <v>130</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -3626,15 +3621,15 @@
     <col min="3" max="3" width="22.0272727272727" customWidth="1"/>
     <col min="4" max="4" width="11.8181818181818" customWidth="1"/>
     <col min="5" max="5" width="21.9090909090909" customWidth="1"/>
-    <col min="6" max="6" width="18.2909090909091" style="8" customWidth="1"/>
-    <col min="7" max="7" width="27.5818181818182" style="9" customWidth="1"/>
-    <col min="8" max="8" width="15.6181818181818" style="8" customWidth="1"/>
-    <col min="9" max="9" width="21.8090909090909" style="10" customWidth="1"/>
-    <col min="10" max="10" width="21.8090909090909" style="11" customWidth="1"/>
-    <col min="11" max="11" width="21.8090909090909" style="8" customWidth="1"/>
-    <col min="12" max="12" width="25.3454545454545" style="8" customWidth="1"/>
+    <col min="6" max="6" width="18.2909090909091" style="9" customWidth="1"/>
+    <col min="7" max="7" width="27.5818181818182" style="10" customWidth="1"/>
+    <col min="8" max="8" width="15.6181818181818" style="9" customWidth="1"/>
+    <col min="9" max="9" width="21.8090909090909" style="11" customWidth="1"/>
+    <col min="10" max="10" width="21.8090909090909" style="12" customWidth="1"/>
+    <col min="11" max="11" width="21.8090909090909" style="9" customWidth="1"/>
+    <col min="12" max="12" width="25.3454545454545" style="9" customWidth="1"/>
     <col min="13" max="13" width="19.0363636363636" customWidth="1"/>
-    <col min="14" max="14" width="19.0363636363636" style="4" customWidth="1"/>
+    <col min="14" max="14" width="19.0363636363636" style="5" customWidth="1"/>
     <col min="15" max="15" width="28.6363636363636" customWidth="1"/>
     <col min="16" max="16" width="14.4363636363636" customWidth="1"/>
     <col min="17" max="17" width="11.0090909090909" customWidth="1"/>
@@ -3658,28 +3653,28 @@
       <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="19" t="s">
         <v>160</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -3711,49 +3706,49 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="str">
+      <c r="B2" s="20" t="str">
         <f>VLOOKUP(C2,$C$39:$D$55,2,0)</f>
         <v>005693</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <v>399.82</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="23">
         <v>1.4256</v>
       </c>
-      <c r="H2" s="21">
+      <c r="H2" s="22">
         <f t="shared" ref="H2:H17" si="0">F2*0.2</f>
         <v>79.964</v>
       </c>
-      <c r="I2" s="23">
+      <c r="I2" s="24">
         <v>1.4484</v>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f t="shared" ref="J2:J17" si="1">I2*F2</f>
         <v>579.099288</v>
       </c>
-      <c r="K2" s="21">
+      <c r="K2" s="22">
         <f t="shared" ref="K2:K17" si="2">F2*G2</f>
         <v>569.983392</v>
       </c>
-      <c r="L2" s="21">
+      <c r="L2" s="22">
         <f t="shared" ref="L2:L17" si="3">J2-K2</f>
         <v>9.11589600000002</v>
       </c>
-      <c r="M2" s="25">
+      <c r="M2" s="26">
         <f t="shared" ref="M2:M17" si="4">L2/K2</f>
         <v>0.015993265993266</v>
       </c>
-      <c r="N2" s="26">
+      <c r="N2" s="27">
         <v>1</v>
       </c>
       <c r="O2" s="2" t="s">
@@ -3792,39 +3787,39 @@
       <c r="D3" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="22">
         <v>479.56</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="23">
         <v>2.5023</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="22">
         <f t="shared" si="0"/>
         <v>95.912</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="24">
         <v>2.4685</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="25">
         <f t="shared" si="1"/>
         <v>1183.79386</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="22">
         <f t="shared" si="2"/>
         <v>1200.002988</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="22">
         <f t="shared" si="3"/>
         <v>-16.209128</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="26">
         <f t="shared" si="4"/>
         <v>-0.0135075730328098</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="27">
         <v>1</v>
       </c>
       <c r="O3" s="2" t="s">
@@ -3863,39 +3858,39 @@
       <c r="D4" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="22">
         <v>383.5</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="23">
         <v>2.556</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="22">
         <f t="shared" si="0"/>
         <v>76.7</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="24">
         <v>2.636</v>
       </c>
-      <c r="J4" s="24">
+      <c r="J4" s="25">
         <f t="shared" si="1"/>
         <v>1010.906</v>
       </c>
-      <c r="K4" s="21">
+      <c r="K4" s="22">
         <f t="shared" si="2"/>
         <v>980.226</v>
       </c>
-      <c r="L4" s="21">
+      <c r="L4" s="22">
         <f t="shared" si="3"/>
         <v>30.6800000000001</v>
       </c>
-      <c r="M4" s="25">
+      <c r="M4" s="26">
         <f t="shared" si="4"/>
         <v>0.0312989045383412</v>
       </c>
-      <c r="N4" s="26">
+      <c r="N4" s="27">
         <v>1</v>
       </c>
       <c r="O4" s="2" t="s">
@@ -3934,39 +3929,39 @@
       <c r="D5" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="22">
         <v>416.65</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="23">
         <v>2.4001</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="22">
         <f t="shared" si="0"/>
         <v>83.33</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="24">
         <v>2.3958</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="25">
         <f t="shared" si="1"/>
         <v>998.21007</v>
       </c>
-      <c r="K5" s="21">
+      <c r="K5" s="22">
         <f t="shared" si="2"/>
         <v>1000.001665</v>
       </c>
-      <c r="L5" s="21">
+      <c r="L5" s="22">
         <f t="shared" si="3"/>
         <v>-1.79159500000014</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="26">
         <f t="shared" si="4"/>
         <v>-0.00179159201699943</v>
       </c>
-      <c r="N5" s="26">
+      <c r="N5" s="27">
         <v>1</v>
       </c>
       <c r="O5" s="2" t="s">
@@ -4005,39 +4000,39 @@
       <c r="D6" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="22">
         <v>233.16</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="23">
         <v>2.5733</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="22">
         <f t="shared" si="0"/>
         <v>46.632</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="24">
         <v>2.5423</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="25">
         <f t="shared" si="1"/>
         <v>592.762668</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="22">
         <f t="shared" si="2"/>
         <v>599.990628</v>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="22">
         <f t="shared" si="3"/>
         <v>-7.22796000000005</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="26">
         <f t="shared" si="4"/>
         <v>-0.0120467881708313</v>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="27">
         <v>1</v>
       </c>
       <c r="O6" s="2" t="s">
@@ -4066,49 +4061,49 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="str">
+      <c r="B7" s="20" t="str">
         <f t="shared" si="5"/>
         <v>014881</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="20" t="s">
         <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <v>1572.57</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <v>1.2718</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="22">
         <f t="shared" si="0"/>
         <v>314.514</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="24">
         <v>1.2077</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="25">
         <f t="shared" si="1"/>
         <v>1899.192789</v>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="22">
         <f t="shared" si="2"/>
         <v>1999.994526</v>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="22">
         <f t="shared" si="3"/>
         <v>-100.801737</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="26">
         <f t="shared" si="4"/>
         <v>-0.0504010064475547</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="27">
         <v>0</v>
       </c>
       <c r="O7" s="2" t="s">
@@ -4137,49 +4132,49 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="19" t="str">
+      <c r="B8" s="20" t="str">
         <f t="shared" si="5"/>
         <v>017470</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="20" t="s">
         <v>75</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="22">
         <v>433.92</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="23">
         <v>2.1663</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="22">
         <f t="shared" si="0"/>
         <v>86.784</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="24">
         <v>2.1024</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="25">
         <f t="shared" si="1"/>
         <v>912.273408</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="22">
         <f t="shared" si="2"/>
         <v>940.000896</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="22">
         <f t="shared" si="3"/>
         <v>-27.7274880000002</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="26">
         <f t="shared" si="4"/>
         <v>-0.0294972995429998</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="27">
         <v>1</v>
       </c>
       <c r="O8" s="2" t="s">
@@ -4208,49 +4203,49 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="str">
+      <c r="B9" s="20" t="str">
         <f t="shared" si="5"/>
         <v>018345</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="20" t="s">
         <v>83</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="22">
         <v>1545.12</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="23">
         <v>1.2944</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="22">
         <f t="shared" si="0"/>
         <v>309.024</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="24">
         <v>1.2294</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="25">
         <f t="shared" si="1"/>
         <v>1899.570528</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K9" s="22">
         <f t="shared" si="2"/>
         <v>2000.003328</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="22">
         <f t="shared" si="3"/>
         <v>-100.4328</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="26">
         <f t="shared" si="4"/>
         <v>-0.0502163164400494</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="27">
         <v>0</v>
       </c>
       <c r="O9" s="2" t="s">
@@ -4289,39 +4284,39 @@
       <c r="D10" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="22">
         <v>388.55</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="23">
         <v>2.5737</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="22">
         <f t="shared" si="0"/>
         <v>77.71</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="24">
         <v>2.5857</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="25">
         <f t="shared" si="1"/>
         <v>1004.673735</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="22">
         <f t="shared" si="2"/>
         <v>1000.011135</v>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="22">
         <f t="shared" si="3"/>
         <v>4.6626</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="26">
         <f t="shared" si="4"/>
         <v>0.0046625480825271</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="27">
         <v>1</v>
       </c>
       <c r="O10" s="2" t="s">
@@ -4350,49 +4345,49 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="str">
+      <c r="B11" s="20" t="str">
         <f t="shared" si="5"/>
         <v>020482</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="20" t="s">
         <v>93</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <v>1209.85</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <v>1.6531</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="22">
         <f t="shared" si="0"/>
         <v>241.97</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="24">
         <v>1.57</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="25">
         <f t="shared" si="1"/>
         <v>1899.4645</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K11" s="22">
         <f t="shared" si="2"/>
         <v>2000.003035</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="22">
         <f t="shared" si="3"/>
         <v>-100.538535</v>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="26">
         <f t="shared" si="4"/>
         <v>-0.0502691912165023</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="27">
         <v>0</v>
       </c>
       <c r="O11" s="2" t="s">
@@ -4421,48 +4416,48 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="20" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="22">
         <v>600</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="23">
         <v>1.506</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="22">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="24">
         <v>1.498</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="25">
         <f t="shared" si="1"/>
         <v>898.8</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="22">
         <f t="shared" si="2"/>
         <v>903.6</v>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="22">
         <f t="shared" si="3"/>
         <v>-4.80000000000007</v>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="26">
         <f t="shared" si="4"/>
         <v>-0.00531208499335997</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="27">
         <v>0</v>
       </c>
       <c r="O12" s="2" t="s">
@@ -4491,48 +4486,48 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="20" t="s">
         <v>106</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="22">
         <v>600</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="23">
         <v>1.538</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="22">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="24">
         <v>1.528</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="25">
         <f t="shared" si="1"/>
         <v>916.8</v>
       </c>
-      <c r="K13" s="21">
+      <c r="K13" s="22">
         <f t="shared" si="2"/>
         <v>922.8</v>
       </c>
-      <c r="L13" s="21">
+      <c r="L13" s="22">
         <f t="shared" si="3"/>
         <v>-6</v>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="26">
         <f t="shared" si="4"/>
         <v>-0.00650195058517555</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="27">
         <v>0</v>
       </c>
       <c r="O13" s="2" t="s">
@@ -4561,48 +4556,48 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="20" t="s">
         <v>109</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="22">
         <v>1500</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="23">
         <v>1.609</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="22">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="24">
         <v>1.48</v>
       </c>
-      <c r="J14" s="24">
+      <c r="J14" s="25">
         <f t="shared" si="1"/>
         <v>2220</v>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="22">
         <f t="shared" si="2"/>
         <v>2413.5</v>
       </c>
-      <c r="L14" s="21">
+      <c r="L14" s="22">
         <f t="shared" si="3"/>
         <v>-193.5</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="26">
         <f t="shared" si="4"/>
         <v>-0.0801740211311373</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="27">
         <v>0</v>
       </c>
       <c r="O14" s="2" t="s">
@@ -4631,48 +4626,48 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="20" t="s">
         <v>116</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="22">
         <v>1600</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="23">
         <v>1.123</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="22">
         <f t="shared" si="0"/>
         <v>320</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="24">
         <v>1.061</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="25">
         <f t="shared" si="1"/>
         <v>1697.6</v>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="22">
         <f t="shared" si="2"/>
         <v>1796.8</v>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="22">
         <f t="shared" si="3"/>
         <v>-99.2</v>
       </c>
-      <c r="M15" s="25">
+      <c r="M15" s="26">
         <f t="shared" si="4"/>
         <v>-0.0552092609082814</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="27">
         <v>0</v>
       </c>
       <c r="O15" s="2" t="s">
@@ -4701,48 +4696,48 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="20" t="s">
         <v>121</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="22">
         <v>1500</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <v>0.938</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="22">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="24">
         <v>0.92</v>
       </c>
-      <c r="J16" s="24">
+      <c r="J16" s="25">
         <f t="shared" si="1"/>
         <v>1380</v>
       </c>
-      <c r="K16" s="21">
+      <c r="K16" s="22">
         <f t="shared" si="2"/>
         <v>1407</v>
       </c>
-      <c r="L16" s="21">
+      <c r="L16" s="22">
         <f t="shared" si="3"/>
         <v>-27</v>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="26">
         <f t="shared" si="4"/>
         <v>-0.0191897654584222</v>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="27">
         <v>0</v>
       </c>
       <c r="O16" s="2" t="s">
@@ -4771,48 +4766,48 @@
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="20" t="s">
         <v>128</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="22">
         <v>200</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="23">
         <v>0.786</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="22">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="24">
         <v>0.737</v>
       </c>
-      <c r="J17" s="24">
+      <c r="J17" s="25">
         <f t="shared" si="1"/>
         <v>147.4</v>
       </c>
-      <c r="K17" s="21">
+      <c r="K17" s="22">
         <f t="shared" si="2"/>
         <v>157.2</v>
       </c>
-      <c r="L17" s="21">
+      <c r="L17" s="22">
         <f t="shared" si="3"/>
         <v>-9.80000000000001</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="26">
         <f t="shared" si="4"/>
         <v>-0.0623409669211197</v>
       </c>
-      <c r="N17" s="26">
+      <c r="N17" s="27">
         <v>0</v>
       </c>
       <c r="O17" s="2" t="s">
@@ -4847,13 +4842,13 @@
       <c r="D18" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="12">
         <v>23000</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="9">
         <v>23000</v>
       </c>
     </row>
@@ -4869,30 +4864,30 @@
       <c r="D19" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="21">
         <v>46088.9471296296</v>
       </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="24">
+      <c r="F19" s="22"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="25">
         <v>81070.62</v>
       </c>
-      <c r="K19" s="21">
+      <c r="K19" s="22">
         <f>J19</f>
         <v>81070.62</v>
       </c>
-      <c r="L19" s="21">
+      <c r="L19" s="22">
         <v>1064.62</v>
       </c>
-      <c r="M19" s="25">
+      <c r="M19" s="26">
         <f>L19/K19</f>
         <v>0.0131320076249571</v>
       </c>
-      <c r="N19" s="26">
+      <c r="N19" s="27">
         <v>0</v>
       </c>
       <c r="O19" s="2" t="s">
@@ -4918,83 +4913,83 @@
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="28" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="C22" s="28"/>
-      <c r="J22" s="11">
+      <c r="C22" s="29"/>
+      <c r="J22" s="12">
         <f>SUM(J2:J17)</f>
         <v>19240.546846</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="12">
         <f>SUM(K2:K17)</f>
         <v>19891.117593</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="12">
         <f>SUM(L2:L17)</f>
         <v>-650.570747</v>
       </c>
-      <c r="M22" s="29">
+      <c r="M22" s="30">
         <f>L22/K22</f>
         <v>-0.0327065959948347</v>
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="28" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="C24" s="28"/>
+      <c r="C24" s="29"/>
     </row>
     <row r="25" spans="1:21">
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="28" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="C26" s="28"/>
+      <c r="C26" s="29"/>
     </row>
     <row r="27" spans="1:21">
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="6" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:21">
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="6" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:21">
-      <c r="C30" s="28"/>
+      <c r="C30" s="29"/>
     </row>
     <row r="31" spans="1:21">
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="28" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="C32" s="28"/>
+      <c r="C32" s="29"/>
     </row>
     <row r="33" spans="3:4">
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="6" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="34" spans="3:4">
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="35" spans="3:4">
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="6" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5161,7 +5156,7 @@
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="20" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20" style="5" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -5213,7 +5208,7 @@
       <c r="D2" t="s">
         <v>199</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="5">
         <v>0.3</v>
       </c>
       <c r="F2" t="s">
@@ -5245,7 +5240,7 @@
       <c r="D3" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="5">
         <v>0.5</v>
       </c>
       <c r="F3" t="s">
@@ -5277,7 +5272,7 @@
       <c r="D4" t="s">
         <v>205</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>-0.1</v>
       </c>
       <c r="F4" t="s">
@@ -5309,7 +5304,7 @@
       <c r="D5" t="s">
         <v>207</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>-0.2</v>
       </c>
       <c r="F5" t="s">
@@ -5341,7 +5336,7 @@
       <c r="D6" t="s">
         <v>209</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>-0.3</v>
       </c>
       <c r="F6" t="s">
@@ -5373,7 +5368,7 @@
       <c r="D7" t="s">
         <v>212</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>-0.02</v>
       </c>
       <c r="F7" t="s">
@@ -5405,7 +5400,7 @@
       <c r="D8" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>-0.03</v>
       </c>
       <c r="F8" t="s">
@@ -5437,7 +5432,7 @@
       <c r="D9" t="s">
         <v>216</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>-0.05</v>
       </c>
       <c r="F9" t="s">
@@ -5469,7 +5464,7 @@
       <c r="D10" t="s">
         <v>218</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>0.1</v>
       </c>
       <c r="F10" t="s">
@@ -5501,7 +5496,7 @@
       <c r="D11" t="s">
         <v>220</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>-0.05</v>
       </c>
       <c r="F11" t="s">
@@ -5533,7 +5528,7 @@
       <c r="D12" t="s">
         <v>222</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>-0.01</v>
       </c>
       <c r="F12" t="s">
@@ -5565,7 +5560,7 @@
       <c r="D13" t="s">
         <v>212</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>-0.02</v>
       </c>
       <c r="F13" t="s">
@@ -5597,7 +5592,7 @@
       <c r="D14" t="s">
         <v>224</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>-0.03</v>
       </c>
       <c r="F14" t="s">
@@ -5629,7 +5624,7 @@
       <c r="D15" t="s">
         <v>227</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>0.15</v>
       </c>
       <c r="F15" t="s">
@@ -5661,7 +5656,7 @@
       <c r="D16" t="s">
         <v>229</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>0.3</v>
       </c>
       <c r="F16" t="s">
@@ -5693,7 +5688,7 @@
       <c r="D17" t="s">
         <v>231</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <v>-0.15</v>
       </c>
       <c r="F17" t="s">
@@ -5725,7 +5720,7 @@
       <c r="D18" t="s">
         <v>232</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <v>-0.25</v>
       </c>
       <c r="F18" t="s">
@@ -5757,7 +5752,7 @@
       <c r="D19" t="s">
         <v>233</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <v>-0.35</v>
       </c>
       <c r="F19" t="s">
@@ -5789,7 +5784,7 @@
       <c r="D20" t="s">
         <v>212</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>-0.02</v>
       </c>
       <c r="F20" t="s">
@@ -5821,7 +5816,7 @@
       <c r="D21" t="s">
         <v>214</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <v>-0.03</v>
       </c>
       <c r="F21" t="s">
@@ -5853,7 +5848,7 @@
       <c r="D22" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <v>-0.05</v>
       </c>
       <c r="F22" t="s">
@@ -5885,7 +5880,7 @@
       <c r="D23" t="s">
         <v>235</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <v>0.1</v>
       </c>
       <c r="F23" t="s">
@@ -5917,7 +5912,7 @@
       <c r="D24" t="s">
         <v>236</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <v>0.25</v>
       </c>
       <c r="F24" t="s">
@@ -5949,7 +5944,7 @@
       <c r="D25" t="s">
         <v>207</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="5">
         <v>-0.2</v>
       </c>
       <c r="F25" t="s">
@@ -5981,7 +5976,7 @@
       <c r="D26" t="s">
         <v>209</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="5">
         <v>-0.3</v>
       </c>
       <c r="F26" t="s">
@@ -6013,7 +6008,7 @@
       <c r="D27" t="s">
         <v>238</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <v>-0.4</v>
       </c>
       <c r="F27" t="s">
@@ -6045,7 +6040,7 @@
       <c r="D28" t="s">
         <v>212</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="5">
         <v>-0.02</v>
       </c>
       <c r="F28" t="s">
@@ -6077,7 +6072,7 @@
       <c r="D29" t="s">
         <v>214</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="5">
         <v>-0.03</v>
       </c>
       <c r="F29" t="s">
@@ -6109,7 +6104,7 @@
       <c r="D30" t="s">
         <v>216</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="5">
         <v>-0.05</v>
       </c>
       <c r="F30" t="s">
@@ -6141,7 +6136,7 @@
       <c r="D31" t="s">
         <v>241</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="5">
         <v>0.2</v>
       </c>
       <c r="F31" t="s">
@@ -6173,7 +6168,7 @@
       <c r="D32" t="s">
         <v>243</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="5">
         <v>0</v>
       </c>
       <c r="F32" t="s">
@@ -6205,7 +6200,7 @@
       <c r="D33" t="s">
         <v>245</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="5">
         <v>0</v>
       </c>
       <c r="F33" t="s">
@@ -6237,7 +6232,7 @@
       <c r="D34" t="s">
         <v>247</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="5">
         <v>0</v>
       </c>
       <c r="F34" t="s">
@@ -6257,32 +6252,32 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="6" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="7" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="7" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="7" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="8" t="s">
         <v>254</v>
       </c>
     </row>
@@ -6349,20 +6344,16 @@
       <c r="C2" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>263</v>
-      </c>
+      <c r="D2" s="4"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3">
-        <v>1.464</v>
-      </c>
+      <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6373,22 +6364,18 @@
         <v>148</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>263</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3">
-        <v>1.055</v>
-      </c>
+      <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6399,22 +6386,18 @@
         <v>149</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>263</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3">
-        <v>0.922</v>
-      </c>
+      <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6425,22 +6408,18 @@
         <v>146</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>263</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3">
-        <v>1.511</v>
-      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6451,22 +6430,18 @@
         <v>145</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>263</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3">
-        <v>1.483</v>
-      </c>
+      <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6477,22 +6452,18 @@
         <v>150</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>263</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3">
-        <v>0.717</v>
-      </c>
+      <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6505,20 +6476,16 @@
       <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>263</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3">
-        <v>1.4457</v>
-      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6531,20 +6498,16 @@
       <c r="C9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>263</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3">
-        <v>2.0509</v>
-      </c>
+      <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6557,20 +6520,16 @@
       <c r="C10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>263</v>
-      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3">
-        <v>1.1995</v>
-      </c>
+      <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6583,20 +6542,16 @@
       <c r="C11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>263</v>
-      </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3">
-        <v>1.5315</v>
-      </c>
+      <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6609,20 +6564,16 @@
       <c r="C12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>263</v>
-      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3">
-        <v>1.1781</v>
-      </c>
+      <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6635,20 +6586,16 @@
       <c r="C13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>270</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3">
-        <v>2.5672</v>
-      </c>
+      <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6661,20 +6608,16 @@
       <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>270</v>
-      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3">
-        <v>2.656</v>
-      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6687,20 +6630,16 @@
       <c r="C15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>270</v>
-      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3">
-        <v>2.4976</v>
-      </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6713,20 +6652,16 @@
       <c r="C16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>270</v>
-      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3">
-        <v>2.4192</v>
-      </c>
+      <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6739,20 +6674,16 @@
       <c r="C17" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>270</v>
-      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3">
-        <v>2.6159</v>
-      </c>
+      <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6765,25 +6696,21 @@
       <c r="C18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>263</v>
-      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3">
-        <v>1</v>
-      </c>
+      <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="B27" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -6815,7 +6742,7 @@
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -6824,46 +6751,46 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>10</v>
